--- a/research/traditional_assets/database/data/poland/poland_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_farming_agriculture.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07794310438723719</v>
+        <v>0.07783146248890144</v>
       </c>
       <c r="C2">
-        <v>3.4921262432626</v>
+        <v>3.469423697377207</v>
       </c>
       <c r="D2">
-        <v>3.4881262432626</v>
+        <v>3.500283697377207</v>
       </c>
       <c r="E2">
-        <v>-0.116</v>
+        <v>-0.08114</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.03486</v>
       </c>
       <c r="G2">
         <v>0.004</v>
@@ -1573,28 +1573,28 @@
         <v>0.136</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001753458</v>
       </c>
       <c r="N2">
-        <v>0.136</v>
+        <v>0.134246542</v>
       </c>
       <c r="O2">
-        <v>0.02584</v>
+        <v>0.02550684298</v>
       </c>
       <c r="P2">
-        <v>0.11016</v>
+        <v>0.10873969902</v>
       </c>
       <c r="Q2">
-        <v>0.2591600000000001</v>
+        <v>0.25773969902</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07794310438723719</v>
+        <v>0.07820609342313277</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5935289815946124</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>77.56102512863153</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07783146248890144</v>
+        <v>0.07771982059056569</v>
       </c>
       <c r="C3">
-        <v>3.469423697377207</v>
+        <v>3.446806194655038</v>
       </c>
       <c r="D3">
-        <v>3.500283697377207</v>
+        <v>3.512526194655039</v>
       </c>
       <c r="E3">
-        <v>-0.08114</v>
+        <v>-0.04628</v>
       </c>
       <c r="F3">
-        <v>0.03486</v>
+        <v>0.06972</v>
       </c>
       <c r="G3">
         <v>0.004</v>
@@ -1655,28 +1655,28 @@
         <v>0.136</v>
       </c>
       <c r="M3">
-        <v>0.001753458</v>
+        <v>0.003506916</v>
       </c>
       <c r="N3">
-        <v>0.134246542</v>
+        <v>0.132493084</v>
       </c>
       <c r="O3">
-        <v>0.02550684298</v>
+        <v>0.02517368596</v>
       </c>
       <c r="P3">
-        <v>0.10873969902</v>
+        <v>0.10731939804</v>
       </c>
       <c r="Q3">
-        <v>0.25773969902</v>
+        <v>0.25631939804</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07820609342313277</v>
+        <v>0.07847444958220989</v>
       </c>
       <c r="T3">
-        <v>0.5935289815946124</v>
+        <v>0.5984440188909003</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>77.56102512863153</v>
+        <v>38.78051256431577</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07771982059056569</v>
+        <v>0.07760817869222993</v>
       </c>
       <c r="C4">
-        <v>3.446806194655038</v>
+        <v>3.424274630562033</v>
       </c>
       <c r="D4">
-        <v>3.512526194655039</v>
+        <v>3.524854630562033</v>
       </c>
       <c r="E4">
-        <v>-0.04628</v>
+        <v>-0.01142</v>
       </c>
       <c r="F4">
-        <v>0.06972</v>
+        <v>0.10458</v>
       </c>
       <c r="G4">
         <v>0.004</v>
@@ -1737,28 +1737,28 @@
         <v>0.136</v>
       </c>
       <c r="M4">
-        <v>0.003506916</v>
+        <v>0.005260374</v>
       </c>
       <c r="N4">
-        <v>0.132493084</v>
+        <v>0.130739626</v>
       </c>
       <c r="O4">
-        <v>0.02517368596</v>
+        <v>0.02484052894</v>
       </c>
       <c r="P4">
-        <v>0.10731939804</v>
+        <v>0.10589909706</v>
       </c>
       <c r="Q4">
-        <v>0.25631939804</v>
+        <v>0.25489909706</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07847444958220989</v>
+        <v>0.078748338857969</v>
       </c>
       <c r="T4">
-        <v>0.5984440188909003</v>
+        <v>0.6034603971623692</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.78051256431577</v>
+        <v>25.85367504287718</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07760817869222993</v>
+        <v>0.07749653679389418</v>
       </c>
       <c r="C5">
-        <v>3.424274630562033</v>
+        <v>3.401829913180205</v>
       </c>
       <c r="D5">
-        <v>3.524854630562033</v>
+        <v>3.537269913180205</v>
       </c>
       <c r="E5">
-        <v>-0.01142</v>
+        <v>0.02344</v>
       </c>
       <c r="F5">
-        <v>0.10458</v>
+        <v>0.13944</v>
       </c>
       <c r="G5">
         <v>0.004</v>
@@ -1819,28 +1819,28 @@
         <v>0.136</v>
       </c>
       <c r="M5">
-        <v>0.005260374</v>
+        <v>0.007013832</v>
       </c>
       <c r="N5">
-        <v>0.130739626</v>
+        <v>0.128986168</v>
       </c>
       <c r="O5">
-        <v>0.02484052894</v>
+        <v>0.02450737192</v>
       </c>
       <c r="P5">
-        <v>0.10589909706</v>
+        <v>0.10447879608</v>
       </c>
       <c r="Q5">
-        <v>0.25489909706</v>
+        <v>0.25347879608</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.078748338857969</v>
+        <v>0.07902793416030644</v>
       </c>
       <c r="T5">
-        <v>0.6034603971623692</v>
+        <v>0.6085812833144938</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.85367504287718</v>
+        <v>19.39025628215789</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07749653679389418</v>
+        <v>0.07738489489555843</v>
       </c>
       <c r="C6">
-        <v>3.401829913180205</v>
+        <v>3.379472963430624</v>
       </c>
       <c r="D6">
-        <v>3.537269913180205</v>
+        <v>3.549772963430624</v>
       </c>
       <c r="E6">
-        <v>0.02344</v>
+        <v>0.0583</v>
       </c>
       <c r="F6">
-        <v>0.13944</v>
+        <v>0.1743</v>
       </c>
       <c r="G6">
         <v>0.004</v>
@@ -1901,28 +1901,28 @@
         <v>0.136</v>
       </c>
       <c r="M6">
-        <v>0.007013832</v>
+        <v>0.00876729</v>
       </c>
       <c r="N6">
-        <v>0.128986168</v>
+        <v>0.12723271</v>
       </c>
       <c r="O6">
-        <v>0.02450737192</v>
+        <v>0.0241742149</v>
       </c>
       <c r="P6">
-        <v>0.10447879608</v>
+        <v>0.1030584951</v>
       </c>
       <c r="Q6">
-        <v>0.25347879608</v>
+        <v>0.2520584951</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07902793416030644</v>
+        <v>0.07931341567953519</v>
       </c>
       <c r="T6">
-        <v>0.6085812833144938</v>
+        <v>0.6138099775961368</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.39025628215789</v>
+        <v>15.51220502572631</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07738489489555843</v>
+        <v>0.07727325299722268</v>
       </c>
       <c r="C7">
-        <v>3.379472963430624</v>
+        <v>3.357204715301118</v>
       </c>
       <c r="D7">
-        <v>3.549772963430624</v>
+        <v>3.562364715301118</v>
       </c>
       <c r="E7">
-        <v>0.0583</v>
+        <v>0.09316000000000003</v>
       </c>
       <c r="F7">
-        <v>0.1743</v>
+        <v>0.20916</v>
       </c>
       <c r="G7">
         <v>0.004</v>
@@ -1983,28 +1983,28 @@
         <v>0.136</v>
       </c>
       <c r="M7">
-        <v>0.00876729</v>
+        <v>0.010520748</v>
       </c>
       <c r="N7">
-        <v>0.12723271</v>
+        <v>0.125479252</v>
       </c>
       <c r="O7">
-        <v>0.0241742149</v>
+        <v>0.02384105788</v>
       </c>
       <c r="P7">
-        <v>0.1030584951</v>
+        <v>0.10163819412</v>
       </c>
       <c r="Q7">
-        <v>0.2520584951</v>
+        <v>0.25063819412</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07931341567953519</v>
+        <v>0.07960497127364115</v>
       </c>
       <c r="T7">
-        <v>0.6138099775961368</v>
+        <v>0.6191499206922828</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.51220502572631</v>
+        <v>12.92683752143859</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07727325299722268</v>
+        <v>0.07724666109888695</v>
       </c>
       <c r="C8">
-        <v>3.357204715301118</v>
+        <v>3.325357119067807</v>
       </c>
       <c r="D8">
-        <v>3.562364715301118</v>
+        <v>3.565377119067807</v>
       </c>
       <c r="E8">
-        <v>0.09316000000000001</v>
+        <v>0.12802</v>
       </c>
       <c r="F8">
-        <v>0.20916</v>
+        <v>0.24402</v>
       </c>
       <c r="G8">
         <v>0.004</v>
@@ -2065,45 +2065,45 @@
         <v>0.136</v>
       </c>
       <c r="M8">
-        <v>0.010520748</v>
+        <v>0.012640236</v>
       </c>
       <c r="N8">
-        <v>0.125479252</v>
+        <v>0.123359764</v>
       </c>
       <c r="O8">
-        <v>0.02384105788</v>
+        <v>0.02343835516</v>
       </c>
       <c r="P8">
-        <v>0.10163819412</v>
+        <v>0.09992140884</v>
       </c>
       <c r="Q8">
-        <v>0.25063819412</v>
+        <v>0.24892140884</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07960497127364115</v>
+        <v>0.0799027968805236</v>
       </c>
       <c r="T8">
-        <v>0.6191499206922828</v>
+        <v>0.6246047012743676</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.19</v>
       </c>
       <c r="W8">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>12.92683752143859</v>
+        <v>10.75929278535622</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07724666109888695</v>
+        <v>0.0772573292005512</v>
       </c>
       <c r="C9">
-        <v>3.325357119067807</v>
+        <v>3.289287995262823</v>
       </c>
       <c r="D9">
-        <v>3.565377119067807</v>
+        <v>3.564167995262823</v>
       </c>
       <c r="E9">
-        <v>0.12802</v>
+        <v>0.16288</v>
       </c>
       <c r="F9">
-        <v>0.24402</v>
+        <v>0.27888</v>
       </c>
       <c r="G9">
         <v>0.004</v>
@@ -2147,45 +2147,45 @@
         <v>0.136</v>
       </c>
       <c r="M9">
-        <v>0.012640236</v>
+        <v>0.01492008</v>
       </c>
       <c r="N9">
-        <v>0.123359764</v>
+        <v>0.12107992</v>
       </c>
       <c r="O9">
-        <v>0.02343835516</v>
+        <v>0.0230051848</v>
       </c>
       <c r="P9">
-        <v>0.09992140884</v>
+        <v>0.09807473520000001</v>
       </c>
       <c r="Q9">
-        <v>0.24892140884</v>
+        <v>0.2470747352</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0799027968805236</v>
+        <v>0.08020709695712086</v>
       </c>
       <c r="T9">
-        <v>0.6246047012743676</v>
+        <v>0.6301780640430193</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.19</v>
       </c>
       <c r="W9">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.75929278535622</v>
+        <v>9.115232626098519</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0772573292005512</v>
+        <v>0.07717160730221544</v>
       </c>
       <c r="C10">
-        <v>3.289287995262823</v>
+        <v>3.264166968583451</v>
       </c>
       <c r="D10">
-        <v>3.564167995262823</v>
+        <v>3.573906968583451</v>
       </c>
       <c r="E10">
-        <v>0.16288</v>
+        <v>0.19774</v>
       </c>
       <c r="F10">
-        <v>0.27888</v>
+        <v>0.31374</v>
       </c>
       <c r="G10">
         <v>0.004</v>
@@ -2229,28 +2229,28 @@
         <v>0.136</v>
       </c>
       <c r="M10">
-        <v>0.01492008</v>
+        <v>0.01678509</v>
       </c>
       <c r="N10">
-        <v>0.12107992</v>
+        <v>0.11921491</v>
       </c>
       <c r="O10">
-        <v>0.0230051848</v>
+        <v>0.0226508329</v>
       </c>
       <c r="P10">
-        <v>0.09807473520000001</v>
+        <v>0.09656407710000001</v>
       </c>
       <c r="Q10">
-        <v>0.2470747352</v>
+        <v>0.2455640771</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08020709695712086</v>
+        <v>0.08051808494748948</v>
       </c>
       <c r="T10">
-        <v>0.6301780640430193</v>
+        <v>0.6358739183010919</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.115232626098519</v>
+        <v>8.102429000976462</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07717160730221544</v>
+        <v>0.07715068540387968</v>
       </c>
       <c r="C11">
-        <v>3.264166968583451</v>
+        <v>3.231692017500082</v>
       </c>
       <c r="D11">
-        <v>3.573906968583451</v>
+        <v>3.576292017500082</v>
       </c>
       <c r="E11">
-        <v>0.19774</v>
+        <v>0.2326</v>
       </c>
       <c r="F11">
-        <v>0.31374</v>
+        <v>0.3486</v>
       </c>
       <c r="G11">
         <v>0.004</v>
@@ -2311,45 +2311,45 @@
         <v>0.136</v>
       </c>
       <c r="M11">
-        <v>0.01678509</v>
+        <v>0.01892898</v>
       </c>
       <c r="N11">
-        <v>0.11921491</v>
+        <v>0.11707102</v>
       </c>
       <c r="O11">
-        <v>0.0226508329</v>
+        <v>0.0222434938</v>
       </c>
       <c r="P11">
-        <v>0.09656407710000001</v>
+        <v>0.09482752620000001</v>
       </c>
       <c r="Q11">
-        <v>0.2455640771</v>
+        <v>0.2438275262</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08051808494748948</v>
+        <v>0.08083598378208853</v>
       </c>
       <c r="T11">
-        <v>0.6358739183010919</v>
+        <v>0.641696347098233</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.19</v>
       </c>
       <c r="W11">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.102429000976462</v>
+        <v>7.184750578213936</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07715068540387968</v>
+        <v>0.07707144350554393</v>
       </c>
       <c r="C12">
-        <v>3.231692017500082</v>
+        <v>3.205894348390546</v>
       </c>
       <c r="D12">
-        <v>3.576292017500082</v>
+        <v>3.585354348390546</v>
       </c>
       <c r="E12">
-        <v>0.2326</v>
+        <v>0.26746</v>
       </c>
       <c r="F12">
-        <v>0.3486</v>
+        <v>0.38346</v>
       </c>
       <c r="G12">
         <v>0.004</v>
@@ -2393,28 +2393,28 @@
         <v>0.136</v>
       </c>
       <c r="M12">
-        <v>0.01892898</v>
+        <v>0.020821878</v>
       </c>
       <c r="N12">
-        <v>0.11707102</v>
+        <v>0.115178122</v>
       </c>
       <c r="O12">
-        <v>0.0222434938</v>
+        <v>0.02188384318</v>
       </c>
       <c r="P12">
-        <v>0.09482752620000001</v>
+        <v>0.09329427882000001</v>
       </c>
       <c r="Q12">
-        <v>0.2438275262</v>
+        <v>0.24229427882</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08083598378208853</v>
+        <v>0.08116102641072352</v>
       </c>
       <c r="T12">
-        <v>0.641696347098233</v>
+        <v>0.6476496169919388</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.184750578213935</v>
+        <v>6.531591434739941</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07707144350554393</v>
+        <v>0.07708940160720819</v>
       </c>
       <c r="C13">
-        <v>3.205894348390546</v>
+        <v>3.168976585870857</v>
       </c>
       <c r="D13">
-        <v>3.585354348390546</v>
+        <v>3.583296585870857</v>
       </c>
       <c r="E13">
-        <v>0.26746</v>
+        <v>0.30232</v>
       </c>
       <c r="F13">
-        <v>0.38346</v>
+        <v>0.41832</v>
       </c>
       <c r="G13">
         <v>0.004</v>
@@ -2475,45 +2475,45 @@
         <v>0.136</v>
       </c>
       <c r="M13">
-        <v>0.020821878</v>
+        <v>0.023133096</v>
       </c>
       <c r="N13">
-        <v>0.115178122</v>
+        <v>0.112866904</v>
       </c>
       <c r="O13">
-        <v>0.02188384318</v>
+        <v>0.02144471176</v>
       </c>
       <c r="P13">
-        <v>0.09329427882000001</v>
+        <v>0.09142219224000001</v>
       </c>
       <c r="Q13">
-        <v>0.24229427882</v>
+        <v>0.24042219224</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08116102641072352</v>
+        <v>0.08149345637182748</v>
       </c>
       <c r="T13">
-        <v>0.6476496169919388</v>
+        <v>0.6537381884741379</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.19</v>
       </c>
       <c r="W13">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.531591434739941</v>
+        <v>5.879022851070172</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07708940160720819</v>
+        <v>0.07701825970887244</v>
       </c>
       <c r="C14">
-        <v>3.168976585870857</v>
+        <v>3.142282400486923</v>
       </c>
       <c r="D14">
-        <v>3.583296585870857</v>
+        <v>3.591462400486924</v>
       </c>
       <c r="E14">
-        <v>0.30232</v>
+        <v>0.33718</v>
       </c>
       <c r="F14">
-        <v>0.41832</v>
+        <v>0.45318</v>
       </c>
       <c r="G14">
         <v>0.004</v>
@@ -2557,28 +2557,28 @@
         <v>0.136</v>
       </c>
       <c r="M14">
-        <v>0.023133096</v>
+        <v>0.025060854</v>
       </c>
       <c r="N14">
-        <v>0.112866904</v>
+        <v>0.110939146</v>
       </c>
       <c r="O14">
-        <v>0.02144471176</v>
+        <v>0.02107843774</v>
       </c>
       <c r="P14">
-        <v>0.09142219224000001</v>
+        <v>0.08986070826000001</v>
       </c>
       <c r="Q14">
-        <v>0.24042219224</v>
+        <v>0.23886070826</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08149345637182748</v>
+        <v>0.0818335284010028</v>
       </c>
       <c r="T14">
-        <v>0.6537381884741379</v>
+        <v>0.6599667271168476</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.879022851070172</v>
+        <v>5.426790324064774</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07701825970887244</v>
+        <v>0.07694711781053669</v>
       </c>
       <c r="C15">
-        <v>3.142282400486923</v>
+        <v>3.115625517530571</v>
       </c>
       <c r="D15">
-        <v>3.591462400486924</v>
+        <v>3.599665517530571</v>
       </c>
       <c r="E15">
-        <v>0.33718</v>
+        <v>0.3720400000000001</v>
       </c>
       <c r="F15">
-        <v>0.45318</v>
+        <v>0.4880400000000001</v>
       </c>
       <c r="G15">
         <v>0.004</v>
@@ -2639,28 +2639,28 @@
         <v>0.136</v>
       </c>
       <c r="M15">
-        <v>0.025060854</v>
+        <v>0.02698861200000001</v>
       </c>
       <c r="N15">
-        <v>0.110939146</v>
+        <v>0.109011388</v>
       </c>
       <c r="O15">
-        <v>0.02107843774</v>
+        <v>0.02071216372</v>
       </c>
       <c r="P15">
-        <v>0.08986070826000001</v>
+        <v>0.08829922428</v>
       </c>
       <c r="Q15">
-        <v>0.23886070826</v>
+        <v>0.23729922428</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0818335284010028</v>
+        <v>0.0821815090820194</v>
       </c>
       <c r="T15">
-        <v>0.6599667271168476</v>
+        <v>0.6663401154954341</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.426790324064774</v>
+        <v>5.039162443774432</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07694711781053669</v>
+        <v>0.07687597591220093</v>
       </c>
       <c r="C16">
-        <v>3.115625517530571</v>
+        <v>3.089006193189944</v>
       </c>
       <c r="D16">
-        <v>3.599665517530571</v>
+        <v>3.607906193189944</v>
       </c>
       <c r="E16">
-        <v>0.3720400000000001</v>
+        <v>0.4069000000000002</v>
       </c>
       <c r="F16">
-        <v>0.4880400000000001</v>
+        <v>0.5229000000000001</v>
       </c>
       <c r="G16">
         <v>0.004</v>
@@ -2721,28 +2721,28 @@
         <v>0.136</v>
       </c>
       <c r="M16">
-        <v>0.02698861200000001</v>
+        <v>0.02891637000000001</v>
       </c>
       <c r="N16">
-        <v>0.109011388</v>
+        <v>0.10708363</v>
       </c>
       <c r="O16">
-        <v>0.02071216372</v>
+        <v>0.0203458897</v>
       </c>
       <c r="P16">
-        <v>0.08829922428</v>
+        <v>0.0867377403</v>
       </c>
       <c r="Q16">
-        <v>0.23729922428</v>
+        <v>0.2357377403</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0821815090820194</v>
+        <v>0.0825376775437658</v>
       </c>
       <c r="T16">
-        <v>0.6663401154954341</v>
+        <v>0.6728634659535168</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.039162443774432</v>
+        <v>4.703218280856137</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07687597591220093</v>
+        <v>0.07712883401386518</v>
       </c>
       <c r="C17">
-        <v>3.089006193189944</v>
+        <v>3.025026427334982</v>
       </c>
       <c r="D17">
-        <v>3.607906193189944</v>
+        <v>3.578786427334982</v>
       </c>
       <c r="E17">
-        <v>0.4069</v>
+        <v>0.44176</v>
       </c>
       <c r="F17">
-        <v>0.5229</v>
+        <v>0.55776</v>
       </c>
       <c r="G17">
         <v>0.004</v>
@@ -2803,45 +2803,45 @@
         <v>0.136</v>
       </c>
       <c r="M17">
-        <v>0.02891637</v>
+        <v>0.032238528</v>
       </c>
       <c r="N17">
-        <v>0.10708363</v>
+        <v>0.103761472</v>
       </c>
       <c r="O17">
-        <v>0.0203458897</v>
+        <v>0.01971467968</v>
       </c>
       <c r="P17">
-        <v>0.0867377403</v>
+        <v>0.08404679232000001</v>
       </c>
       <c r="Q17">
-        <v>0.2357377403</v>
+        <v>0.23304679232</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0825376775437658</v>
+        <v>0.08290232620698236</v>
       </c>
       <c r="T17">
-        <v>0.6728634659535168</v>
+        <v>0.679542134279649</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.19</v>
       </c>
       <c r="W17">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.703218280856138</v>
+        <v>4.218554891836252</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07712883401386518</v>
+        <v>0.07755989211552942</v>
       </c>
       <c r="C18">
-        <v>3.025026427334982</v>
+        <v>2.941593690437224</v>
       </c>
       <c r="D18">
-        <v>3.578786427334982</v>
+        <v>3.530213690437224</v>
       </c>
       <c r="E18">
-        <v>0.44176</v>
+        <v>0.47662</v>
       </c>
       <c r="F18">
-        <v>0.55776</v>
+        <v>0.59262</v>
       </c>
       <c r="G18">
         <v>0.004</v>
@@ -2885,45 +2885,45 @@
         <v>0.136</v>
       </c>
       <c r="M18">
-        <v>0.032238528</v>
+        <v>0.03632760600000001</v>
       </c>
       <c r="N18">
-        <v>0.103761472</v>
+        <v>0.099672394</v>
       </c>
       <c r="O18">
-        <v>0.01971467968</v>
+        <v>0.01893775486</v>
       </c>
       <c r="P18">
-        <v>0.08404679232000001</v>
+        <v>0.08073463913999999</v>
       </c>
       <c r="Q18">
-        <v>0.23304679232</v>
+        <v>0.22973463914</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08290232620698236</v>
+        <v>0.08327576158497521</v>
       </c>
       <c r="T18">
-        <v>0.679542134279649</v>
+        <v>0.686381734372676</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V18">
         <v>0.19</v>
       </c>
       <c r="W18">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.218554891836252</v>
+        <v>3.743709398301666</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07755989211552942</v>
+        <v>0.07753735021719366</v>
       </c>
       <c r="C19">
-        <v>2.941593690437224</v>
+        <v>2.909241074247428</v>
       </c>
       <c r="D19">
-        <v>3.530213690437224</v>
+        <v>3.532721074247429</v>
       </c>
       <c r="E19">
-        <v>0.47662</v>
+        <v>0.5114800000000002</v>
       </c>
       <c r="F19">
-        <v>0.59262</v>
+        <v>0.6274800000000001</v>
       </c>
       <c r="G19">
         <v>0.004</v>
@@ -2967,28 +2967,28 @@
         <v>0.136</v>
       </c>
       <c r="M19">
-        <v>0.03632760600000001</v>
+        <v>0.03846452400000001</v>
       </c>
       <c r="N19">
-        <v>0.099672394</v>
+        <v>0.09753547600000001</v>
       </c>
       <c r="O19">
-        <v>0.01893775486</v>
+        <v>0.01853174044</v>
       </c>
       <c r="P19">
-        <v>0.08073463913999999</v>
+        <v>0.07900373556000001</v>
       </c>
       <c r="Q19">
-        <v>0.22973463914</v>
+        <v>0.22800373556</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08327576158497521</v>
+        <v>0.08365830514291911</v>
       </c>
       <c r="T19">
-        <v>0.686381734372676</v>
+        <v>0.6933881539801671</v>
       </c>
       <c r="U19">
         <v>0.0613</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.743709398301666</v>
+        <v>3.535725542840462</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07753735021719368</v>
+        <v>0.07794572831885793</v>
       </c>
       <c r="C20">
-        <v>2.909241074247426</v>
+        <v>2.829501520992316</v>
       </c>
       <c r="D20">
-        <v>3.532721074247426</v>
+        <v>3.487841520992316</v>
       </c>
       <c r="E20">
-        <v>0.51148</v>
+        <v>0.54634</v>
       </c>
       <c r="F20">
-        <v>0.62748</v>
+        <v>0.66234</v>
       </c>
       <c r="G20">
         <v>0.004</v>
@@ -3049,45 +3049,45 @@
         <v>0.136</v>
       </c>
       <c r="M20">
-        <v>0.038464524</v>
+        <v>0.042455994</v>
       </c>
       <c r="N20">
-        <v>0.09753547600000001</v>
+        <v>0.09354400600000001</v>
       </c>
       <c r="O20">
-        <v>0.01853174044</v>
+        <v>0.01777336114</v>
       </c>
       <c r="P20">
-        <v>0.07900373556000001</v>
+        <v>0.07577064486000001</v>
       </c>
       <c r="Q20">
-        <v>0.22800373556</v>
+        <v>0.22477064486</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08365830514291911</v>
+        <v>0.08405029422081225</v>
       </c>
       <c r="T20">
-        <v>0.6933881539801671</v>
+        <v>0.7005675716026579</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.535725542840463</v>
+        <v>3.203316827301229</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07794572831885793</v>
+        <v>0.07794586642052218</v>
       </c>
       <c r="C21">
-        <v>2.829501520992316</v>
+        <v>2.794626536897243</v>
       </c>
       <c r="D21">
-        <v>3.487841520992316</v>
+        <v>3.487826536897243</v>
       </c>
       <c r="E21">
-        <v>0.54634</v>
+        <v>0.5812</v>
       </c>
       <c r="F21">
-        <v>0.66234</v>
+        <v>0.6972</v>
       </c>
       <c r="G21">
         <v>0.004</v>
@@ -3131,28 +3131,28 @@
         <v>0.136</v>
       </c>
       <c r="M21">
-        <v>0.042455994</v>
+        <v>0.04469052</v>
       </c>
       <c r="N21">
-        <v>0.09354400600000001</v>
+        <v>0.09130948</v>
       </c>
       <c r="O21">
-        <v>0.01777336114</v>
+        <v>0.0173488012</v>
       </c>
       <c r="P21">
-        <v>0.07577064486000001</v>
+        <v>0.0739606788</v>
       </c>
       <c r="Q21">
-        <v>0.22477064486</v>
+        <v>0.2229606788</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08405029422081225</v>
+        <v>0.08445208302565271</v>
       </c>
       <c r="T21">
-        <v>0.7005675716026579</v>
+        <v>0.7079264746657111</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.203316827301229</v>
+        <v>3.043150985936167</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07794586642052218</v>
+        <v>0.07927278452218643</v>
       </c>
       <c r="C22">
-        <v>2.794626536897243</v>
+        <v>2.621503161640657</v>
       </c>
       <c r="D22">
-        <v>3.487826536897243</v>
+        <v>3.349563161640657</v>
       </c>
       <c r="E22">
-        <v>0.5812</v>
+        <v>0.6160600000000002</v>
       </c>
       <c r="F22">
-        <v>0.6972</v>
+        <v>0.7320600000000002</v>
       </c>
       <c r="G22">
         <v>0.004</v>
@@ -3213,45 +3213,45 @@
         <v>0.136</v>
       </c>
       <c r="M22">
-        <v>0.04469052</v>
+        <v>0.05263511400000002</v>
       </c>
       <c r="N22">
-        <v>0.09130948</v>
+        <v>0.083364886</v>
       </c>
       <c r="O22">
-        <v>0.0173488012</v>
+        <v>0.01583932834</v>
       </c>
       <c r="P22">
-        <v>0.0739606788</v>
+        <v>0.06752555766</v>
       </c>
       <c r="Q22">
-        <v>0.2229606788</v>
+        <v>0.21652555766</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08445208302565271</v>
+        <v>0.08486404369897016</v>
       </c>
       <c r="T22">
-        <v>0.7079264746657111</v>
+        <v>0.7154716790721326</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0.19</v>
       </c>
       <c r="W22">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.043150985936167</v>
+        <v>2.583826454712342</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07927278452218643</v>
+        <v>0.08003108262385068</v>
       </c>
       <c r="C23">
-        <v>2.621503161640657</v>
+        <v>2.512442546521727</v>
       </c>
       <c r="D23">
-        <v>3.349563161640657</v>
+        <v>3.275362546521727</v>
       </c>
       <c r="E23">
-        <v>0.6160600000000001</v>
+        <v>0.6509200000000001</v>
       </c>
       <c r="F23">
-        <v>0.73206</v>
+        <v>0.76692</v>
       </c>
       <c r="G23">
         <v>0.004</v>
@@ -3295,45 +3295,45 @@
         <v>0.136</v>
       </c>
       <c r="M23">
-        <v>0.05263511400000001</v>
+        <v>0.05813253600000001</v>
       </c>
       <c r="N23">
-        <v>0.083364886</v>
+        <v>0.077867464</v>
       </c>
       <c r="O23">
-        <v>0.01583932834</v>
+        <v>0.01479481816</v>
       </c>
       <c r="P23">
-        <v>0.06752555766</v>
+        <v>0.06307264584</v>
       </c>
       <c r="Q23">
-        <v>0.21652555766</v>
+        <v>0.21207264584</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08486404369897016</v>
+        <v>0.08528656746647523</v>
       </c>
       <c r="T23">
-        <v>0.7154716790721326</v>
+        <v>0.723210350258206</v>
       </c>
       <c r="U23">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V23">
         <v>0.19</v>
       </c>
       <c r="W23">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.583826454712343</v>
+        <v>2.339481628670044</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08003108262385068</v>
+        <v>0.08012599072551493</v>
       </c>
       <c r="C24">
-        <v>2.512442546521727</v>
+        <v>2.468526480404414</v>
       </c>
       <c r="D24">
-        <v>3.275362546521727</v>
+        <v>3.266306480404414</v>
       </c>
       <c r="E24">
-        <v>0.6509200000000001</v>
+        <v>0.6857800000000001</v>
       </c>
       <c r="F24">
-        <v>0.76692</v>
+        <v>0.80178</v>
       </c>
       <c r="G24">
         <v>0.004</v>
@@ -3377,28 +3377,28 @@
         <v>0.136</v>
       </c>
       <c r="M24">
-        <v>0.05813253600000001</v>
+        <v>0.06077492400000001</v>
       </c>
       <c r="N24">
-        <v>0.077867464</v>
+        <v>0.075225076</v>
       </c>
       <c r="O24">
-        <v>0.01479481816</v>
+        <v>0.01429276444</v>
       </c>
       <c r="P24">
-        <v>0.06307264584</v>
+        <v>0.06093231156</v>
       </c>
       <c r="Q24">
-        <v>0.21207264584</v>
+        <v>0.20993231156</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08528656746647523</v>
+        <v>0.08572006587729211</v>
       </c>
       <c r="T24">
-        <v>0.723210350258206</v>
+        <v>0.7311500258906709</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.339481628670044</v>
+        <v>2.237765036119173</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08012599072551493</v>
+        <v>0.08022089882717917</v>
       </c>
       <c r="C25">
-        <v>2.468526480404414</v>
+        <v>2.42466035453114</v>
       </c>
       <c r="D25">
-        <v>3.266306480404414</v>
+        <v>3.25730035453114</v>
       </c>
       <c r="E25">
-        <v>0.6857800000000001</v>
+        <v>0.7206400000000002</v>
       </c>
       <c r="F25">
-        <v>0.80178</v>
+        <v>0.8366400000000002</v>
       </c>
       <c r="G25">
         <v>0.004</v>
@@ -3459,28 +3459,28 @@
         <v>0.136</v>
       </c>
       <c r="M25">
-        <v>0.06077492400000001</v>
+        <v>0.06341731200000002</v>
       </c>
       <c r="N25">
-        <v>0.075225076</v>
+        <v>0.07258268799999999</v>
       </c>
       <c r="O25">
-        <v>0.01429276444</v>
+        <v>0.01379071072</v>
       </c>
       <c r="P25">
-        <v>0.06093231156</v>
+        <v>0.05879197727999999</v>
       </c>
       <c r="Q25">
-        <v>0.20993231156</v>
+        <v>0.20779197728</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08572006587729211</v>
+        <v>0.08616497214102523</v>
       </c>
       <c r="T25">
-        <v>0.7311500258906709</v>
+        <v>0.7392986403555691</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.237765036119173</v>
+        <v>2.144524826280874</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08022089882717917</v>
+        <v>0.08031580692884342</v>
       </c>
       <c r="C26">
-        <v>2.42466035453114</v>
+        <v>2.380843756939893</v>
       </c>
       <c r="D26">
-        <v>3.25730035453114</v>
+        <v>3.248343756939893</v>
       </c>
       <c r="E26">
-        <v>0.7206400000000001</v>
+        <v>0.7555000000000001</v>
       </c>
       <c r="F26">
-        <v>0.8366400000000001</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="G26">
         <v>0.004</v>
@@ -3541,28 +3541,28 @@
         <v>0.136</v>
       </c>
       <c r="M26">
-        <v>0.063417312</v>
+        <v>0.06605970000000001</v>
       </c>
       <c r="N26">
-        <v>0.07258268800000001</v>
+        <v>0.0699403</v>
       </c>
       <c r="O26">
-        <v>0.01379071072</v>
+        <v>0.013288657</v>
       </c>
       <c r="P26">
-        <v>0.05879197728</v>
+        <v>0.056651643</v>
       </c>
       <c r="Q26">
-        <v>0.20779197728</v>
+        <v>0.205651643</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08616497214102523</v>
+        <v>0.08662174257179123</v>
       </c>
       <c r="T26">
-        <v>0.7392986403555691</v>
+        <v>0.7476645512061979</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.144524826280874</v>
+        <v>2.058743833229639</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08031580692884342</v>
+        <v>0.08340123503050767</v>
       </c>
       <c r="C27">
-        <v>2.380843756939893</v>
+        <v>2.079435833623113</v>
       </c>
       <c r="D27">
-        <v>3.248343756939893</v>
+        <v>2.981795833623113</v>
       </c>
       <c r="E27">
-        <v>0.7555000000000001</v>
+        <v>0.7903600000000001</v>
       </c>
       <c r="F27">
-        <v>0.8715000000000001</v>
+        <v>0.9063600000000001</v>
       </c>
       <c r="G27">
         <v>0.004</v>
@@ -3623,45 +3623,45 @@
         <v>0.136</v>
       </c>
       <c r="M27">
-        <v>0.06605970000000001</v>
+        <v>0.0815724</v>
       </c>
       <c r="N27">
-        <v>0.0699403</v>
+        <v>0.05442760000000001</v>
       </c>
       <c r="O27">
-        <v>0.013288657</v>
+        <v>0.010341244</v>
       </c>
       <c r="P27">
-        <v>0.056651643</v>
+        <v>0.04408635600000001</v>
       </c>
       <c r="Q27">
-        <v>0.205651643</v>
+        <v>0.193086356</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08662174257179123</v>
+        <v>0.08709085814933469</v>
       </c>
       <c r="T27">
-        <v>0.7476645512061979</v>
+        <v>0.7562565677554924</v>
       </c>
       <c r="U27">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V27">
         <v>0.19</v>
       </c>
       <c r="W27">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.058743833229639</v>
+        <v>1.667230582893234</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08340123503050767</v>
+        <v>0.08361116313217193</v>
       </c>
       <c r="C28">
-        <v>2.079435833623113</v>
+        <v>2.028020861835686</v>
       </c>
       <c r="D28">
-        <v>2.981795833623113</v>
+        <v>2.965240861835686</v>
       </c>
       <c r="E28">
-        <v>0.7903600000000001</v>
+        <v>0.8252200000000002</v>
       </c>
       <c r="F28">
-        <v>0.9063600000000001</v>
+        <v>0.9412200000000002</v>
       </c>
       <c r="G28">
         <v>0.004</v>
@@ -3705,28 +3705,28 @@
         <v>0.136</v>
       </c>
       <c r="M28">
-        <v>0.0815724</v>
+        <v>0.08470980000000002</v>
       </c>
       <c r="N28">
-        <v>0.05442760000000001</v>
+        <v>0.05129019999999999</v>
       </c>
       <c r="O28">
-        <v>0.010341244</v>
+        <v>0.009745137999999999</v>
       </c>
       <c r="P28">
-        <v>0.04408635600000001</v>
+        <v>0.04154506199999999</v>
       </c>
       <c r="Q28">
-        <v>0.193086356</v>
+        <v>0.190545062</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08709085814933469</v>
+        <v>0.08757282620845469</v>
       </c>
       <c r="T28">
-        <v>0.7562565677554924</v>
+        <v>0.7650839820184662</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.667230582893234</v>
+        <v>1.605481302045336</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08361116313217193</v>
+        <v>0.08382109123383616</v>
       </c>
       <c r="C29">
-        <v>2.028020861835686</v>
+        <v>1.976788701939644</v>
       </c>
       <c r="D29">
-        <v>2.965240861835686</v>
+        <v>2.948868701939644</v>
       </c>
       <c r="E29">
-        <v>0.8252200000000002</v>
+        <v>0.8600800000000002</v>
       </c>
       <c r="F29">
-        <v>0.9412200000000002</v>
+        <v>0.9760800000000002</v>
       </c>
       <c r="G29">
         <v>0.004</v>
@@ -3787,28 +3787,28 @@
         <v>0.136</v>
       </c>
       <c r="M29">
-        <v>0.08470980000000002</v>
+        <v>0.08784720000000001</v>
       </c>
       <c r="N29">
-        <v>0.05129019999999999</v>
+        <v>0.0481528</v>
       </c>
       <c r="O29">
-        <v>0.009745137999999999</v>
+        <v>0.009149032</v>
       </c>
       <c r="P29">
-        <v>0.04154506199999999</v>
+        <v>0.03900376799999999</v>
       </c>
       <c r="Q29">
-        <v>0.190545062</v>
+        <v>0.188003768</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08757282620845469</v>
+        <v>0.08806818226921689</v>
       </c>
       <c r="T29">
-        <v>0.7650839820184662</v>
+        <v>0.7741566022331892</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.605481302045336</v>
+        <v>1.548142684115145</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08382109123383616</v>
+        <v>0.09819756593649727</v>
       </c>
       <c r="C30">
-        <v>1.976788701939644</v>
+        <v>1.13283889906056</v>
       </c>
       <c r="D30">
-        <v>2.948868701939644</v>
+        <v>2.13977889906056</v>
       </c>
       <c r="E30">
-        <v>0.8600800000000002</v>
+        <v>0.8949400000000002</v>
       </c>
       <c r="F30">
-        <v>0.9760800000000002</v>
+        <v>1.01094</v>
       </c>
       <c r="G30">
         <v>0.004</v>
@@ -3869,45 +3869,45 @@
         <v>0.136</v>
       </c>
       <c r="M30">
-        <v>0.08784720000000001</v>
+        <v>0.148405992</v>
       </c>
       <c r="N30">
-        <v>0.0481528</v>
+        <v>-0.01240599200000003</v>
       </c>
       <c r="O30">
-        <v>0.009149032</v>
+        <v>-0.002357138480000006</v>
       </c>
       <c r="P30">
-        <v>0.03900376799999999</v>
+        <v>-0.01004885352000003</v>
       </c>
       <c r="Q30">
-        <v>0.188003768</v>
+        <v>0.13895114648</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08806818226921689</v>
+        <v>0.08878601846202899</v>
       </c>
       <c r="T30">
-        <v>0.7741566022331892</v>
+        <v>0.7873040241982009</v>
       </c>
       <c r="U30">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.19</v>
+        <v>0.1741169588354626</v>
       </c>
       <c r="W30">
-        <v>0.07290000000000001</v>
+        <v>0.1212396304429541</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.548142684115145</v>
+        <v>0.9164050465024348</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09819756593649726</v>
+        <v>0.09920756593649727</v>
       </c>
       <c r="C31">
-        <v>1.132838899060561</v>
+        <v>1.057513158857742</v>
       </c>
       <c r="D31">
-        <v>2.139778899060561</v>
+        <v>2.099313158857742</v>
       </c>
       <c r="E31">
-        <v>0.89494</v>
+        <v>0.9298000000000001</v>
       </c>
       <c r="F31">
-        <v>1.01094</v>
+        <v>1.0458</v>
       </c>
       <c r="G31">
         <v>0.004</v>
@@ -3951,37 +3951,37 @@
         <v>0.136</v>
       </c>
       <c r="M31">
-        <v>0.148405992</v>
+        <v>0.15352344</v>
       </c>
       <c r="N31">
-        <v>-0.012405992</v>
+        <v>-0.01752344</v>
       </c>
       <c r="O31">
-        <v>-0.002357138480000001</v>
+        <v>-0.0033294536</v>
       </c>
       <c r="P31">
-        <v>-0.01004885352</v>
+        <v>-0.0141939864</v>
       </c>
       <c r="Q31">
-        <v>0.13895114648</v>
+        <v>0.1348060136</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08878601846202899</v>
+        <v>0.08940010444005797</v>
       </c>
       <c r="T31">
-        <v>0.7873040241982009</v>
+        <v>0.7985512245438894</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.1741169588354627</v>
+        <v>0.1683130602076139</v>
       </c>
       <c r="W31">
-        <v>0.1212396304429541</v>
+        <v>0.1220916427615223</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.916405046502435</v>
+        <v>0.8858582116190206</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09920756593649727</v>
+        <v>0.1002175659364973</v>
       </c>
       <c r="C32">
-        <v>1.057513158857742</v>
+        <v>0.9836895217681931</v>
       </c>
       <c r="D32">
-        <v>2.099313158857742</v>
+        <v>2.060349521768193</v>
       </c>
       <c r="E32">
-        <v>0.9298000000000001</v>
+        <v>0.96466</v>
       </c>
       <c r="F32">
-        <v>1.0458</v>
+        <v>1.08066</v>
       </c>
       <c r="G32">
         <v>0.004</v>
@@ -4033,37 +4033,37 @@
         <v>0.136</v>
       </c>
       <c r="M32">
-        <v>0.15352344</v>
+        <v>0.158640888</v>
       </c>
       <c r="N32">
-        <v>-0.01752344</v>
+        <v>-0.022640888</v>
       </c>
       <c r="O32">
-        <v>-0.0033294536</v>
+        <v>-0.00430176872</v>
       </c>
       <c r="P32">
-        <v>-0.0141939864</v>
+        <v>-0.01833911928</v>
       </c>
       <c r="Q32">
-        <v>0.1348060136</v>
+        <v>0.13066088072</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08940010444005797</v>
+        <v>0.09003199001165302</v>
       </c>
       <c r="T32">
-        <v>0.7985512245438894</v>
+        <v>0.8101244306966995</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1683130602076139</v>
+        <v>0.1628836066525296</v>
       </c>
       <c r="W32">
-        <v>0.1220916427615223</v>
+        <v>0.1228886865434087</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8858582116190206</v>
+        <v>0.8572821402764714</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1002175659364973</v>
+        <v>0.1012275659364973</v>
       </c>
       <c r="C33">
-        <v>0.9836895217681931</v>
+        <v>0.9112858739130805</v>
       </c>
       <c r="D33">
-        <v>2.060349521768193</v>
+        <v>2.022805873913081</v>
       </c>
       <c r="E33">
-        <v>0.96466</v>
+        <v>0.9995200000000001</v>
       </c>
       <c r="F33">
-        <v>1.08066</v>
+        <v>1.11552</v>
       </c>
       <c r="G33">
         <v>0.004</v>
@@ -4115,37 +4115,37 @@
         <v>0.136</v>
       </c>
       <c r="M33">
-        <v>0.158640888</v>
+        <v>0.163758336</v>
       </c>
       <c r="N33">
-        <v>-0.022640888</v>
+        <v>-0.02775833600000002</v>
       </c>
       <c r="O33">
-        <v>-0.00430176872</v>
+        <v>-0.005274083840000004</v>
       </c>
       <c r="P33">
-        <v>-0.01833911928</v>
+        <v>-0.02248425216000002</v>
       </c>
       <c r="Q33">
-        <v>0.13066088072</v>
+        <v>0.12651574784</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09003199001165302</v>
+        <v>0.09068246045300087</v>
       </c>
       <c r="T33">
-        <v>0.8101244306966995</v>
+        <v>0.8220380252657686</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.1628836066525296</v>
+        <v>0.157793493944638</v>
       </c>
       <c r="W33">
-        <v>0.1228886865434087</v>
+        <v>0.1236359150889271</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8572821402764714</v>
+        <v>0.8304920733928316</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1012275659364973</v>
+        <v>0.1022375659364973</v>
       </c>
       <c r="C34">
-        <v>0.9112858739130805</v>
+        <v>0.8402259794145996</v>
       </c>
       <c r="D34">
-        <v>2.022805873913081</v>
+        <v>1.9866059794146</v>
       </c>
       <c r="E34">
-        <v>0.9995200000000001</v>
+        <v>1.03438</v>
       </c>
       <c r="F34">
-        <v>1.11552</v>
+        <v>1.15038</v>
       </c>
       <c r="G34">
         <v>0.004</v>
@@ -4197,37 +4197,37 @@
         <v>0.136</v>
       </c>
       <c r="M34">
-        <v>0.163758336</v>
+        <v>0.168875784</v>
       </c>
       <c r="N34">
-        <v>-0.02775833600000002</v>
+        <v>-0.03287578400000002</v>
       </c>
       <c r="O34">
-        <v>-0.005274083840000004</v>
+        <v>-0.006246398960000003</v>
       </c>
       <c r="P34">
-        <v>-0.02248425216000002</v>
+        <v>-0.02662938504000002</v>
       </c>
       <c r="Q34">
-        <v>0.12651574784</v>
+        <v>0.12237061496</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09068246045300087</v>
+        <v>0.09135234792244865</v>
       </c>
       <c r="T34">
-        <v>0.8220380252657686</v>
+        <v>0.8343072495234666</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.157793493944638</v>
+        <v>0.1530118729160126</v>
       </c>
       <c r="W34">
-        <v>0.1236359150889271</v>
+        <v>0.1243378570559294</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8304920733928316</v>
+        <v>0.8053256469263822</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1022375659364973</v>
+        <v>0.1220440384916597</v>
       </c>
       <c r="C35">
-        <v>0.8402259794145996</v>
+        <v>0.2892907873390764</v>
       </c>
       <c r="D35">
-        <v>1.9866059794146</v>
+        <v>1.470530787339076</v>
       </c>
       <c r="E35">
-        <v>1.03438</v>
+        <v>1.06924</v>
       </c>
       <c r="F35">
-        <v>1.15038</v>
+        <v>1.18524</v>
       </c>
       <c r="G35">
         <v>0.004</v>
@@ -4279,45 +4279,45 @@
         <v>0.136</v>
       </c>
       <c r="M35">
-        <v>0.168875784</v>
+        <v>0.237996192</v>
       </c>
       <c r="N35">
-        <v>-0.03287578400000002</v>
+        <v>-0.101996192</v>
       </c>
       <c r="O35">
-        <v>-0.006246398960000003</v>
+        <v>-0.01937927648</v>
       </c>
       <c r="P35">
-        <v>-0.02662938504000002</v>
+        <v>-0.08261691552000001</v>
       </c>
       <c r="Q35">
-        <v>0.12237061496</v>
+        <v>0.06638308448000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09135234792244865</v>
+        <v>0.09270385706545912</v>
       </c>
       <c r="T35">
-        <v>0.8343072495234666</v>
+        <v>0.8590606141081101</v>
       </c>
       <c r="U35">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1530118729160126</v>
+        <v>0.1085731657420804</v>
       </c>
       <c r="W35">
-        <v>0.1243378570559294</v>
+        <v>0.1789985083189903</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8053256469263822</v>
+        <v>0.5714377144320023</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1220440384916597</v>
+        <v>0.1235940384916597</v>
       </c>
       <c r="C36">
-        <v>0.2892907873390764</v>
+        <v>0.2251313350343871</v>
       </c>
       <c r="D36">
-        <v>1.470530787339076</v>
+        <v>1.441231335034387</v>
       </c>
       <c r="E36">
-        <v>1.06924</v>
+        <v>1.1041</v>
       </c>
       <c r="F36">
-        <v>1.18524</v>
+        <v>1.2201</v>
       </c>
       <c r="G36">
         <v>0.004</v>
@@ -4361,37 +4361,37 @@
         <v>0.136</v>
       </c>
       <c r="M36">
-        <v>0.237996192</v>
+        <v>0.24499608</v>
       </c>
       <c r="N36">
-        <v>-0.101996192</v>
+        <v>-0.10899608</v>
       </c>
       <c r="O36">
-        <v>-0.01937927648</v>
+        <v>-0.02070925520000001</v>
       </c>
       <c r="P36">
-        <v>-0.08261691552000001</v>
+        <v>-0.08828682480000002</v>
       </c>
       <c r="Q36">
-        <v>0.06638308448000001</v>
+        <v>0.0607131752</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09270385706545912</v>
+        <v>0.0934254548664662</v>
       </c>
       <c r="T36">
-        <v>0.8590606141081101</v>
+        <v>0.8722769312482348</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1085731657420804</v>
+        <v>0.1054710752923067</v>
       </c>
       <c r="W36">
-        <v>0.1789985083189903</v>
+        <v>0.1796214080813048</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5714377144320023</v>
+        <v>0.555110922591088</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1235940384916597</v>
+        <v>0.1251440384916597</v>
       </c>
       <c r="C37">
-        <v>0.2251313350343871</v>
+        <v>0.1621166228244946</v>
       </c>
       <c r="D37">
-        <v>1.441231335034387</v>
+        <v>1.413076622824495</v>
       </c>
       <c r="E37">
-        <v>1.1041</v>
+        <v>1.13896</v>
       </c>
       <c r="F37">
-        <v>1.2201</v>
+        <v>1.25496</v>
       </c>
       <c r="G37">
         <v>0.004</v>
@@ -4443,37 +4443,37 @@
         <v>0.136</v>
       </c>
       <c r="M37">
-        <v>0.24499608</v>
+        <v>0.2519959680000001</v>
       </c>
       <c r="N37">
-        <v>-0.10899608</v>
+        <v>-0.1159959680000001</v>
       </c>
       <c r="O37">
-        <v>-0.02070925520000001</v>
+        <v>-0.02203923392000001</v>
       </c>
       <c r="P37">
-        <v>-0.08828682480000002</v>
+        <v>-0.09395673408000005</v>
       </c>
       <c r="Q37">
-        <v>0.0607131752</v>
+        <v>0.05504326591999997</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0934254548664662</v>
+        <v>0.09416960259875473</v>
       </c>
       <c r="T37">
-        <v>0.8722769312482348</v>
+        <v>0.8859062582989885</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1054710752923067</v>
+        <v>0.1025413232008537</v>
       </c>
       <c r="W37">
-        <v>0.1796214080813048</v>
+        <v>0.1802097023012686</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.555110922591088</v>
+        <v>0.5396911747413354</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1251440384916597</v>
+        <v>0.1266940384916597</v>
       </c>
       <c r="C38">
-        <v>0.1621166228244948</v>
+        <v>0.1001808480675728</v>
       </c>
       <c r="D38">
-        <v>1.413076622824495</v>
+        <v>1.386000848067573</v>
       </c>
       <c r="E38">
-        <v>1.13896</v>
+        <v>1.17382</v>
       </c>
       <c r="F38">
-        <v>1.25496</v>
+        <v>1.28982</v>
       </c>
       <c r="G38">
         <v>0.004</v>
@@ -4525,37 +4525,37 @@
         <v>0.136</v>
       </c>
       <c r="M38">
-        <v>0.251995968</v>
+        <v>0.258995856</v>
       </c>
       <c r="N38">
-        <v>-0.115995968</v>
+        <v>-0.122995856</v>
       </c>
       <c r="O38">
-        <v>-0.02203923392</v>
+        <v>-0.02336921264</v>
       </c>
       <c r="P38">
-        <v>-0.09395673408000001</v>
+        <v>-0.09962664336000002</v>
       </c>
       <c r="Q38">
-        <v>0.05504326592000001</v>
+        <v>0.04937335664</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0941696025987547</v>
+        <v>0.09493737406857622</v>
       </c>
       <c r="T38">
-        <v>0.8859062582989883</v>
+        <v>0.8999682623989724</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1025413232008538</v>
+        <v>0.09976993608731716</v>
       </c>
       <c r="W38">
-        <v>0.1802097023012686</v>
+        <v>0.1807661968336667</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5396911747413355</v>
+        <v>0.5251049267753535</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1266940384916597</v>
+        <v>0.1282440384916597</v>
       </c>
       <c r="C39">
-        <v>0.1001808480675728</v>
+        <v>0.03926315664671831</v>
       </c>
       <c r="D39">
-        <v>1.386000848067573</v>
+        <v>1.359943156646718</v>
       </c>
       <c r="E39">
-        <v>1.17382</v>
+        <v>1.20868</v>
       </c>
       <c r="F39">
-        <v>1.28982</v>
+        <v>1.32468</v>
       </c>
       <c r="G39">
         <v>0.004</v>
@@ -4607,37 +4607,37 @@
         <v>0.136</v>
       </c>
       <c r="M39">
-        <v>0.258995856</v>
+        <v>0.265995744</v>
       </c>
       <c r="N39">
-        <v>-0.122995856</v>
+        <v>-0.129995744</v>
       </c>
       <c r="O39">
-        <v>-0.02336921264</v>
+        <v>-0.02469919136</v>
       </c>
       <c r="P39">
-        <v>-0.09962664336000002</v>
+        <v>-0.10529655264</v>
       </c>
       <c r="Q39">
-        <v>0.04937335664</v>
+        <v>0.04370344736000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09493737406857622</v>
+        <v>0.09572991236000487</v>
       </c>
       <c r="T39">
-        <v>0.8999682623989724</v>
+        <v>0.9144838795344397</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.09976993608731716</v>
+        <v>0.0971444114534404</v>
       </c>
       <c r="W39">
-        <v>0.1807661968336667</v>
+        <v>0.1812934021801492</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5251049267753535</v>
+        <v>0.5112863760707389</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1282440384916597</v>
+        <v>0.1436201604396716</v>
       </c>
       <c r="C40">
-        <v>0.03926315664671831</v>
+        <v>-0.2093631234838527</v>
       </c>
       <c r="D40">
-        <v>1.359943156646718</v>
+        <v>1.146176876516148</v>
       </c>
       <c r="E40">
-        <v>1.20868</v>
+        <v>1.24354</v>
       </c>
       <c r="F40">
-        <v>1.32468</v>
+        <v>1.35954</v>
       </c>
       <c r="G40">
         <v>0.004</v>
@@ -4689,45 +4689,45 @@
         <v>0.136</v>
       </c>
       <c r="M40">
-        <v>0.265995744</v>
+        <v>0.3205795320000001</v>
       </c>
       <c r="N40">
-        <v>-0.129995744</v>
+        <v>-0.184579532</v>
       </c>
       <c r="O40">
-        <v>-0.02469919136</v>
+        <v>-0.03507011108000001</v>
       </c>
       <c r="P40">
-        <v>-0.10529655264</v>
+        <v>-0.14950942092</v>
       </c>
       <c r="Q40">
-        <v>0.04370344736000001</v>
+        <v>-0.0005094209200000033</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09572991236000487</v>
+        <v>0.09683716001838505</v>
       </c>
       <c r="T40">
-        <v>0.9144838795344397</v>
+        <v>0.9347635092469887</v>
       </c>
       <c r="U40">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.0971444114534404</v>
+        <v>0.08060402309153036</v>
       </c>
       <c r="W40">
-        <v>0.1812934021801492</v>
+        <v>0.2167935713550171</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.5112863760707389</v>
+        <v>0.4242317004817387</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1436201604396716</v>
+        <v>0.1455201604396716</v>
       </c>
       <c r="C41">
-        <v>-0.2093631234838527</v>
+        <v>-0.2660615968254403</v>
       </c>
       <c r="D41">
-        <v>1.146176876516148</v>
+        <v>1.12433840317456</v>
       </c>
       <c r="E41">
-        <v>1.24354</v>
+        <v>1.2784</v>
       </c>
       <c r="F41">
-        <v>1.35954</v>
+        <v>1.3944</v>
       </c>
       <c r="G41">
         <v>0.004</v>
@@ -4771,37 +4771,37 @@
         <v>0.136</v>
       </c>
       <c r="M41">
-        <v>0.3205795320000001</v>
+        <v>0.32879952</v>
       </c>
       <c r="N41">
-        <v>-0.184579532</v>
+        <v>-0.19279952</v>
       </c>
       <c r="O41">
-        <v>-0.03507011108000001</v>
+        <v>-0.0366319088</v>
       </c>
       <c r="P41">
-        <v>-0.14950942092</v>
+        <v>-0.1561676112</v>
       </c>
       <c r="Q41">
-        <v>-0.0005094209200000033</v>
+        <v>-0.007167611199999979</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09683716001838505</v>
+        <v>0.09768777935202479</v>
       </c>
       <c r="T41">
-        <v>0.9347635092469887</v>
+        <v>0.9503429010677718</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08060402309153036</v>
+        <v>0.07858892251424211</v>
       </c>
       <c r="W41">
-        <v>0.2167935713550171</v>
+        <v>0.2172687320711417</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4242317004817387</v>
+        <v>0.4136259079696953</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1455201604396716</v>
+        <v>0.1474201604396716</v>
       </c>
       <c r="C42">
-        <v>-0.2660615968254403</v>
+        <v>-0.3219434389165079</v>
       </c>
       <c r="D42">
-        <v>1.12433840317456</v>
+        <v>1.103316561083492</v>
       </c>
       <c r="E42">
-        <v>1.2784</v>
+        <v>1.31326</v>
       </c>
       <c r="F42">
-        <v>1.3944</v>
+        <v>1.42926</v>
       </c>
       <c r="G42">
         <v>0.004</v>
@@ -4853,37 +4853,37 @@
         <v>0.136</v>
       </c>
       <c r="M42">
-        <v>0.32879952</v>
+        <v>0.3370195080000001</v>
       </c>
       <c r="N42">
-        <v>-0.19279952</v>
+        <v>-0.2010195080000001</v>
       </c>
       <c r="O42">
-        <v>-0.0366319088</v>
+        <v>-0.03819370652000002</v>
       </c>
       <c r="P42">
-        <v>-0.1561676112</v>
+        <v>-0.1628258014800001</v>
       </c>
       <c r="Q42">
-        <v>-0.007167611199999979</v>
+        <v>-0.01382580148000004</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09768777935202479</v>
+        <v>0.09856723323934724</v>
       </c>
       <c r="T42">
-        <v>0.9503429010677718</v>
+        <v>0.9664504078655307</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.07858892251424211</v>
+        <v>0.07667211952608985</v>
       </c>
       <c r="W42">
-        <v>0.2172687320711417</v>
+        <v>0.217720714215748</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4136259079696953</v>
+        <v>0.4035374711899467</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1474201604396716</v>
+        <v>0.1493201604396716</v>
       </c>
       <c r="C43">
-        <v>-0.3219434389165079</v>
+        <v>-0.3770536148933921</v>
       </c>
       <c r="D43">
-        <v>1.103316561083492</v>
+        <v>1.083066385106608</v>
       </c>
       <c r="E43">
-        <v>1.31326</v>
+        <v>1.34812</v>
       </c>
       <c r="F43">
-        <v>1.42926</v>
+        <v>1.46412</v>
       </c>
       <c r="G43">
         <v>0.004</v>
@@ -4935,37 +4935,37 @@
         <v>0.136</v>
       </c>
       <c r="M43">
-        <v>0.3370195080000001</v>
+        <v>0.3452394960000001</v>
       </c>
       <c r="N43">
-        <v>-0.2010195080000001</v>
+        <v>-0.2092394960000001</v>
       </c>
       <c r="O43">
-        <v>-0.03819370652000002</v>
+        <v>-0.03975550424000002</v>
       </c>
       <c r="P43">
-        <v>-0.1628258014800001</v>
+        <v>-0.1694839917600001</v>
       </c>
       <c r="Q43">
-        <v>-0.01382580148000004</v>
+        <v>-0.02048399176000004</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09856723323934724</v>
+        <v>0.09947701312278427</v>
       </c>
       <c r="T43">
-        <v>0.9664504078655307</v>
+        <v>0.9831133459321778</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07667211952608985</v>
+        <v>0.07484659287070676</v>
       </c>
       <c r="W43">
-        <v>0.217720714215748</v>
+        <v>0.2181511734010874</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4035374711899467</v>
+        <v>0.3939294361616146</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1493201604396716</v>
+        <v>0.1512201604396715</v>
       </c>
       <c r="C44">
-        <v>-0.3770536148933914</v>
+        <v>-0.4314338482445839</v>
       </c>
       <c r="D44">
-        <v>1.083066385106609</v>
+        <v>1.063546151755416</v>
       </c>
       <c r="E44">
-        <v>1.34812</v>
+        <v>1.38298</v>
       </c>
       <c r="F44">
-        <v>1.46412</v>
+        <v>1.49898</v>
       </c>
       <c r="G44">
         <v>0.004</v>
@@ -5017,37 +5017,37 @@
         <v>0.136</v>
       </c>
       <c r="M44">
-        <v>0.345239496</v>
+        <v>0.353459484</v>
       </c>
       <c r="N44">
-        <v>-0.209239496</v>
+        <v>-0.217459484</v>
       </c>
       <c r="O44">
-        <v>-0.03975550424</v>
+        <v>-0.04131730196</v>
       </c>
       <c r="P44">
-        <v>-0.16948399176</v>
+        <v>-0.17614218204</v>
       </c>
       <c r="Q44">
-        <v>-0.02048399175999999</v>
+        <v>-0.02714218203999996</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09947701312278426</v>
+        <v>0.1004187151073945</v>
       </c>
       <c r="T44">
-        <v>0.9831133459321777</v>
+        <v>1.000360948492391</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.07484659287070677</v>
+        <v>0.07310597443185314</v>
       </c>
       <c r="W44">
-        <v>0.2181511734010874</v>
+        <v>0.218561611228969</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3939294361616146</v>
+        <v>0.3847682864834375</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1512201604396715</v>
+        <v>0.1531201604396716</v>
       </c>
       <c r="C45">
-        <v>-0.4314338482445839</v>
+        <v>-0.4851229077619825</v>
       </c>
       <c r="D45">
-        <v>1.063546151755416</v>
+        <v>1.044717092238018</v>
       </c>
       <c r="E45">
-        <v>1.38298</v>
+        <v>1.41784</v>
       </c>
       <c r="F45">
-        <v>1.49898</v>
+        <v>1.53384</v>
       </c>
       <c r="G45">
         <v>0.004</v>
@@ -5099,37 +5099,37 @@
         <v>0.136</v>
       </c>
       <c r="M45">
-        <v>0.353459484</v>
+        <v>0.3616794720000001</v>
       </c>
       <c r="N45">
-        <v>-0.217459484</v>
+        <v>-0.225679472</v>
       </c>
       <c r="O45">
-        <v>-0.04131730196</v>
+        <v>-0.04287909968000001</v>
       </c>
       <c r="P45">
-        <v>-0.17614218204</v>
+        <v>-0.18280037232</v>
       </c>
       <c r="Q45">
-        <v>-0.02714218203999996</v>
+        <v>-0.03380037232000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1004187151073945</v>
+        <v>0.1013940493057408</v>
       </c>
       <c r="T45">
-        <v>1.000360948492391</v>
+        <v>1.018224536858327</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.07310597443185314</v>
+        <v>0.07144447501294737</v>
       </c>
       <c r="W45">
-        <v>0.218561611228969</v>
+        <v>0.218953392791947</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3847682864834375</v>
+        <v>0.376023552699723</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1531201604396716</v>
+        <v>0.1550201604396716</v>
       </c>
       <c r="C46">
-        <v>-0.4851229077619825</v>
+        <v>-0.5381568645412225</v>
       </c>
       <c r="D46">
-        <v>1.044717092238018</v>
+        <v>1.026543135458778</v>
       </c>
       <c r="E46">
-        <v>1.41784</v>
+        <v>1.4527</v>
       </c>
       <c r="F46">
-        <v>1.53384</v>
+        <v>1.5687</v>
       </c>
       <c r="G46">
         <v>0.004</v>
@@ -5181,37 +5181,37 @@
         <v>0.136</v>
       </c>
       <c r="M46">
-        <v>0.3616794720000001</v>
+        <v>0.3698994600000001</v>
       </c>
       <c r="N46">
-        <v>-0.225679472</v>
+        <v>-0.2338994600000001</v>
       </c>
       <c r="O46">
-        <v>-0.04287909968000001</v>
+        <v>-0.04444089740000001</v>
       </c>
       <c r="P46">
-        <v>-0.18280037232</v>
+        <v>-0.1894585626</v>
       </c>
       <c r="Q46">
-        <v>-0.03380037232000002</v>
+        <v>-0.04045856260000003</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1013940493057408</v>
+        <v>0.1024048502022089</v>
       </c>
       <c r="T46">
-        <v>1.018224536858327</v>
+        <v>1.036737710255751</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07144447501294737</v>
+        <v>0.06985682001265965</v>
       </c>
       <c r="W46">
-        <v>0.218953392791947</v>
+        <v>0.2193277618410149</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.376023552699723</v>
+        <v>0.3676674737508403</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1550201604396716</v>
+        <v>0.1569201604396716</v>
       </c>
       <c r="C47">
-        <v>-0.5381568645412225</v>
+        <v>-0.5905693226159259</v>
       </c>
       <c r="D47">
-        <v>1.026543135458778</v>
+        <v>1.008990677384074</v>
       </c>
       <c r="E47">
-        <v>1.4527</v>
+        <v>1.48756</v>
       </c>
       <c r="F47">
-        <v>1.5687</v>
+        <v>1.60356</v>
       </c>
       <c r="G47">
         <v>0.004</v>
@@ -5263,37 +5263,37 @@
         <v>0.136</v>
       </c>
       <c r="M47">
-        <v>0.3698994600000001</v>
+        <v>0.378119448</v>
       </c>
       <c r="N47">
-        <v>-0.2338994600000001</v>
+        <v>-0.242119448</v>
       </c>
       <c r="O47">
-        <v>-0.04444089740000001</v>
+        <v>-0.04600269512000001</v>
       </c>
       <c r="P47">
-        <v>-0.1894585626</v>
+        <v>-0.19611675288</v>
       </c>
       <c r="Q47">
-        <v>-0.04045856260000003</v>
+        <v>-0.04711675288</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1024048502022089</v>
+        <v>0.1034530881689164</v>
       </c>
       <c r="T47">
-        <v>1.036737710255751</v>
+        <v>1.055936556741969</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06985682001265965</v>
+        <v>0.06833819349064532</v>
       </c>
       <c r="W47">
-        <v>0.2193277618410149</v>
+        <v>0.2196858539749058</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3676674737508403</v>
+        <v>0.3596747025823438</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1569201604396716</v>
+        <v>0.1588201604396716</v>
       </c>
       <c r="C48">
-        <v>-0.5905693226159259</v>
+        <v>-0.6423916263285727</v>
       </c>
       <c r="D48">
-        <v>1.008990677384074</v>
+        <v>0.9920283736714275</v>
       </c>
       <c r="E48">
-        <v>1.48756</v>
+        <v>1.52242</v>
       </c>
       <c r="F48">
-        <v>1.60356</v>
+        <v>1.63842</v>
       </c>
       <c r="G48">
         <v>0.004</v>
@@ -5345,37 +5345,37 @@
         <v>0.136</v>
       </c>
       <c r="M48">
-        <v>0.378119448</v>
+        <v>0.3863394360000001</v>
       </c>
       <c r="N48">
-        <v>-0.242119448</v>
+        <v>-0.2503394360000001</v>
       </c>
       <c r="O48">
-        <v>-0.04600269512000001</v>
+        <v>-0.04756449284000001</v>
       </c>
       <c r="P48">
-        <v>-0.19611675288</v>
+        <v>-0.2027749431600001</v>
       </c>
       <c r="Q48">
-        <v>-0.04711675288</v>
+        <v>-0.05377494316000003</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1034530881689164</v>
+        <v>0.1045408822853111</v>
       </c>
       <c r="T48">
-        <v>1.055936556741969</v>
+        <v>1.075859888001251</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06833819349064532</v>
+        <v>0.06688418937382307</v>
       </c>
       <c r="W48">
-        <v>0.2196858539749058</v>
+        <v>0.2200287081456525</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3596747025823438</v>
+        <v>0.3520220493359109</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1588201604396716</v>
+        <v>0.1607201604396716</v>
       </c>
       <c r="C49">
-        <v>-0.6423916263285727</v>
+        <v>-0.6936530471303232</v>
       </c>
       <c r="D49">
-        <v>0.9920283736714275</v>
+        <v>0.9756269528696772</v>
       </c>
       <c r="E49">
-        <v>1.52242</v>
+        <v>1.55728</v>
       </c>
       <c r="F49">
-        <v>1.63842</v>
+        <v>1.67328</v>
       </c>
       <c r="G49">
         <v>0.004</v>
@@ -5427,37 +5427,37 @@
         <v>0.136</v>
       </c>
       <c r="M49">
-        <v>0.3863394360000001</v>
+        <v>0.3945594240000001</v>
       </c>
       <c r="N49">
-        <v>-0.2503394360000001</v>
+        <v>-0.2585594240000001</v>
       </c>
       <c r="O49">
-        <v>-0.04756449284000001</v>
+        <v>-0.04912629056000002</v>
       </c>
       <c r="P49">
-        <v>-0.2027749431600001</v>
+        <v>-0.2094331334400001</v>
       </c>
       <c r="Q49">
-        <v>-0.05377494316000003</v>
+        <v>-0.06043313344000006</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1045408822853111</v>
+        <v>0.1056705146369517</v>
       </c>
       <c r="T49">
-        <v>1.075859888001251</v>
+        <v>1.096549501232044</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06688418937382307</v>
+        <v>0.06549076876186842</v>
       </c>
       <c r="W49">
-        <v>0.2200287081456525</v>
+        <v>0.2203572767259514</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3520220493359109</v>
+        <v>0.3446882566414127</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1607201604396716</v>
+        <v>0.1626201604396716</v>
       </c>
       <c r="C50">
-        <v>-0.6936530471303229</v>
+        <v>-0.7443809521518165</v>
       </c>
       <c r="D50">
-        <v>0.9756269528696772</v>
+        <v>0.9597590478481834</v>
       </c>
       <c r="E50">
-        <v>1.55728</v>
+        <v>1.59214</v>
       </c>
       <c r="F50">
-        <v>1.67328</v>
+        <v>1.70814</v>
       </c>
       <c r="G50">
         <v>0.004</v>
@@ -5509,37 +5509,37 @@
         <v>0.136</v>
       </c>
       <c r="M50">
-        <v>0.394559424</v>
+        <v>0.402779412</v>
       </c>
       <c r="N50">
-        <v>-0.258559424</v>
+        <v>-0.266779412</v>
       </c>
       <c r="O50">
-        <v>-0.04912629056000001</v>
+        <v>-0.05068808828</v>
       </c>
       <c r="P50">
-        <v>-0.20943313344</v>
+        <v>-0.21609132372</v>
       </c>
       <c r="Q50">
-        <v>-0.06043313344000001</v>
+        <v>-0.06709132371999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1056705146369517</v>
+        <v>0.1068444462964998</v>
       </c>
       <c r="T50">
-        <v>1.096549501232044</v>
+        <v>1.118050471844438</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06549076876186843</v>
+        <v>0.06415422246060581</v>
       </c>
       <c r="W50">
-        <v>0.2203572767259514</v>
+        <v>0.2206724343437892</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3446882566414128</v>
+        <v>0.3376538024242411</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1626201604396716</v>
+        <v>0.1645201604396716</v>
       </c>
       <c r="C51">
-        <v>-0.7443809521518165</v>
+        <v>-0.7946009565871056</v>
       </c>
       <c r="D51">
-        <v>0.9597590478481834</v>
+        <v>0.9443990434128945</v>
       </c>
       <c r="E51">
-        <v>1.59214</v>
+        <v>1.627</v>
       </c>
       <c r="F51">
-        <v>1.70814</v>
+        <v>1.743</v>
       </c>
       <c r="G51">
         <v>0.004</v>
@@ -5591,37 +5591,37 @@
         <v>0.136</v>
       </c>
       <c r="M51">
-        <v>0.402779412</v>
+        <v>0.4109994</v>
       </c>
       <c r="N51">
-        <v>-0.266779412</v>
+        <v>-0.2749994</v>
       </c>
       <c r="O51">
-        <v>-0.05068808828</v>
+        <v>-0.052249886</v>
       </c>
       <c r="P51">
-        <v>-0.21609132372</v>
+        <v>-0.222749514</v>
       </c>
       <c r="Q51">
-        <v>-0.06709132371999998</v>
+        <v>-0.07374951399999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1068444462964998</v>
+        <v>0.1080653352224298</v>
       </c>
       <c r="T51">
-        <v>1.118050471844438</v>
+        <v>1.140411481281326</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06415422246060581</v>
+        <v>0.0628711380113937</v>
       </c>
       <c r="W51">
-        <v>0.2206724343437892</v>
+        <v>0.2209749856569134</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3376538024242411</v>
+        <v>0.3309007263757563</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1645201604396716</v>
+        <v>0.1664201604396716</v>
       </c>
       <c r="C52">
-        <v>-0.7946009565871056</v>
+        <v>-0.8443370616755408</v>
       </c>
       <c r="D52">
-        <v>0.9443990434128945</v>
+        <v>0.9295229383244594</v>
       </c>
       <c r="E52">
-        <v>1.627</v>
+        <v>1.66186</v>
       </c>
       <c r="F52">
-        <v>1.743</v>
+        <v>1.77786</v>
       </c>
       <c r="G52">
         <v>0.004</v>
@@ -5673,37 +5673,37 @@
         <v>0.136</v>
       </c>
       <c r="M52">
-        <v>0.4109994</v>
+        <v>0.4192193880000001</v>
       </c>
       <c r="N52">
-        <v>-0.2749994</v>
+        <v>-0.2832193880000001</v>
       </c>
       <c r="O52">
-        <v>-0.052249886</v>
+        <v>-0.05381168372000002</v>
       </c>
       <c r="P52">
-        <v>-0.222749514</v>
+        <v>-0.2294077042800001</v>
       </c>
       <c r="Q52">
-        <v>-0.07374951399999999</v>
+        <v>-0.08040770428000005</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1080653352224298</v>
+        <v>0.1093360563494181</v>
       </c>
       <c r="T52">
-        <v>1.140411481281326</v>
+        <v>1.163685184980945</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0628711380113937</v>
+        <v>0.06163837059940557</v>
       </c>
       <c r="W52">
-        <v>0.2209749856569134</v>
+        <v>0.2212656722126602</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3309007263757563</v>
+        <v>0.3244124768389767</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1664201604396716</v>
+        <v>0.1683201604396716</v>
       </c>
       <c r="C53">
-        <v>-0.8443370616755408</v>
+        <v>-0.8936117798450141</v>
       </c>
       <c r="D53">
-        <v>0.9295229383244594</v>
+        <v>0.9151082201549861</v>
       </c>
       <c r="E53">
-        <v>1.66186</v>
+        <v>1.69672</v>
       </c>
       <c r="F53">
-        <v>1.77786</v>
+        <v>1.81272</v>
       </c>
       <c r="G53">
         <v>0.004</v>
@@ -5755,37 +5755,37 @@
         <v>0.136</v>
       </c>
       <c r="M53">
-        <v>0.4192193880000001</v>
+        <v>0.427439376</v>
       </c>
       <c r="N53">
-        <v>-0.2832193880000001</v>
+        <v>-0.291439376</v>
       </c>
       <c r="O53">
-        <v>-0.05381168372000002</v>
+        <v>-0.05537348144</v>
       </c>
       <c r="P53">
-        <v>-0.2294077042800001</v>
+        <v>-0.23606589456</v>
       </c>
       <c r="Q53">
-        <v>-0.08040770428000005</v>
+        <v>-0.08706589456</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1093360563494181</v>
+        <v>0.110659724190031</v>
       </c>
       <c r="T53">
-        <v>1.163685184980945</v>
+        <v>1.187928626334715</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06163837059940557</v>
+        <v>0.06045301731864778</v>
       </c>
       <c r="W53">
-        <v>0.2212656722126602</v>
+        <v>0.2215451785162628</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3244124768389767</v>
+        <v>0.3181737753613041</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1683201604396716</v>
+        <v>0.1702201604396716</v>
       </c>
       <c r="C54">
-        <v>-0.8936117798450141</v>
+        <v>-0.9424462483889404</v>
       </c>
       <c r="D54">
-        <v>0.9151082201549861</v>
+        <v>0.9011337516110598</v>
       </c>
       <c r="E54">
-        <v>1.69672</v>
+        <v>1.73158</v>
       </c>
       <c r="F54">
-        <v>1.81272</v>
+        <v>1.84758</v>
       </c>
       <c r="G54">
         <v>0.004</v>
@@ -5837,37 +5837,37 @@
         <v>0.136</v>
       </c>
       <c r="M54">
-        <v>0.427439376</v>
+        <v>0.435659364</v>
       </c>
       <c r="N54">
-        <v>-0.291439376</v>
+        <v>-0.299659364</v>
       </c>
       <c r="O54">
-        <v>-0.05537348144</v>
+        <v>-0.05693527916</v>
       </c>
       <c r="P54">
-        <v>-0.23606589456</v>
+        <v>-0.24272408484</v>
       </c>
       <c r="Q54">
-        <v>-0.08706589456</v>
+        <v>-0.09372408484</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.110659724190031</v>
+        <v>0.1120397183217338</v>
       </c>
       <c r="T54">
-        <v>1.187928626334715</v>
+        <v>1.213203703490773</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06045301731864778</v>
+        <v>0.0593123943503714</v>
       </c>
       <c r="W54">
-        <v>0.2215451785162628</v>
+        <v>0.2218141374121824</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3181737753613041</v>
+        <v>0.3121704965809021</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1702201604396716</v>
+        <v>0.1721201604396716</v>
       </c>
       <c r="C55">
-        <v>-0.9424462483889404</v>
+        <v>-0.9908603328842556</v>
       </c>
       <c r="D55">
-        <v>0.9011337516110598</v>
+        <v>0.8875796671157448</v>
       </c>
       <c r="E55">
-        <v>1.73158</v>
+        <v>1.76644</v>
       </c>
       <c r="F55">
-        <v>1.84758</v>
+        <v>1.88244</v>
       </c>
       <c r="G55">
         <v>0.004</v>
@@ -5919,37 +5919,37 @@
         <v>0.136</v>
       </c>
       <c r="M55">
-        <v>0.435659364</v>
+        <v>0.4438793520000001</v>
       </c>
       <c r="N55">
-        <v>-0.299659364</v>
+        <v>-0.3078793520000001</v>
       </c>
       <c r="O55">
-        <v>-0.05693527916</v>
+        <v>-0.05849707688000002</v>
       </c>
       <c r="P55">
-        <v>-0.24272408484</v>
+        <v>-0.2493822751200001</v>
       </c>
       <c r="Q55">
-        <v>-0.09372408484</v>
+        <v>-0.1003822751200001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1120397183217338</v>
+        <v>0.1134797121982932</v>
       </c>
       <c r="T55">
-        <v>1.213203703490773</v>
+        <v>1.23957769704492</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0593123943503714</v>
+        <v>0.05821401667721637</v>
       </c>
       <c r="W55">
-        <v>0.2218141374121824</v>
+        <v>0.2220731348675124</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3121704965809021</v>
+        <v>0.3063895614590335</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1721201604396716</v>
+        <v>0.1740201604396716</v>
       </c>
       <c r="C56">
-        <v>-0.9908603328842556</v>
+        <v>-1.038872721414555</v>
       </c>
       <c r="D56">
-        <v>0.8875796671157448</v>
+        <v>0.8744272785854456</v>
       </c>
       <c r="E56">
-        <v>1.76644</v>
+        <v>1.8013</v>
       </c>
       <c r="F56">
-        <v>1.88244</v>
+        <v>1.9173</v>
       </c>
       <c r="G56">
         <v>0.004</v>
@@ -6001,37 +6001,37 @@
         <v>0.136</v>
       </c>
       <c r="M56">
-        <v>0.4438793520000001</v>
+        <v>0.4520993400000001</v>
       </c>
       <c r="N56">
-        <v>-0.3078793520000001</v>
+        <v>-0.3160993400000001</v>
       </c>
       <c r="O56">
-        <v>-0.05849707688000002</v>
+        <v>-0.06005887460000001</v>
       </c>
       <c r="P56">
-        <v>-0.2493822751200001</v>
+        <v>-0.2560404654</v>
       </c>
       <c r="Q56">
-        <v>-0.1003822751200001</v>
+        <v>-0.1070404654</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1134797121982932</v>
+        <v>0.1149837058026997</v>
       </c>
       <c r="T56">
-        <v>1.23957769704492</v>
+        <v>1.267123868090363</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05821401667721637</v>
+        <v>0.05715558001035789</v>
       </c>
       <c r="W56">
-        <v>0.2220731348675124</v>
+        <v>0.2223227142335576</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3063895614590335</v>
+        <v>0.3008188421597784</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1740201604396716</v>
+        <v>0.1759201604396716</v>
       </c>
       <c r="C57">
-        <v>-1.038872721414555</v>
+        <v>-1.086501010538227</v>
       </c>
       <c r="D57">
-        <v>0.8744272785854456</v>
+        <v>0.8616589894617732</v>
       </c>
       <c r="E57">
-        <v>1.8013</v>
+        <v>1.83616</v>
       </c>
       <c r="F57">
-        <v>1.9173</v>
+        <v>1.95216</v>
       </c>
       <c r="G57">
         <v>0.004</v>
@@ -6083,37 +6083,37 @@
         <v>0.136</v>
       </c>
       <c r="M57">
-        <v>0.4520993400000001</v>
+        <v>0.4603193280000001</v>
       </c>
       <c r="N57">
-        <v>-0.3160993400000001</v>
+        <v>-0.3243193280000001</v>
       </c>
       <c r="O57">
-        <v>-0.06005887460000001</v>
+        <v>-0.06162067232000001</v>
       </c>
       <c r="P57">
-        <v>-0.2560404654</v>
+        <v>-0.2626986556800001</v>
       </c>
       <c r="Q57">
-        <v>-0.1070404654</v>
+        <v>-0.11369865568</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1149837058026997</v>
+        <v>0.1165560627527611</v>
       </c>
       <c r="T57">
-        <v>1.267123868090363</v>
+        <v>1.295922137819689</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05715558001035789</v>
+        <v>0.05613494465303008</v>
       </c>
       <c r="W57">
-        <v>0.2223227142335576</v>
+        <v>0.2225633800508155</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3008188421597784</v>
+        <v>0.2954470771212109</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1759201604396716</v>
+        <v>0.1778201604396716</v>
       </c>
       <c r="C58">
-        <v>-1.086501010538227</v>
+        <v>-1.133761783833193</v>
       </c>
       <c r="D58">
-        <v>0.8616589894617732</v>
+        <v>0.8492582161668074</v>
       </c>
       <c r="E58">
-        <v>1.83616</v>
+        <v>1.87102</v>
       </c>
       <c r="F58">
-        <v>1.95216</v>
+        <v>1.98702</v>
       </c>
       <c r="G58">
         <v>0.004</v>
@@ -6165,37 +6165,37 @@
         <v>0.136</v>
       </c>
       <c r="M58">
-        <v>0.4603193280000001</v>
+        <v>0.4685393160000001</v>
       </c>
       <c r="N58">
-        <v>-0.3243193280000001</v>
+        <v>-0.3325393160000001</v>
       </c>
       <c r="O58">
-        <v>-0.06162067232000001</v>
+        <v>-0.06318247004000002</v>
       </c>
       <c r="P58">
-        <v>-0.2626986556800001</v>
+        <v>-0.2693568459600001</v>
       </c>
       <c r="Q58">
-        <v>-0.11369865568</v>
+        <v>-0.1203568459600001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1165560627527611</v>
+        <v>0.1182015525842207</v>
       </c>
       <c r="T58">
-        <v>1.295922137819689</v>
+        <v>1.326059861955031</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05613494465303008</v>
+        <v>0.05515012106262604</v>
       </c>
       <c r="W58">
-        <v>0.2225633800508155</v>
+        <v>0.2227956014534328</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2954470771212109</v>
+        <v>0.2902637950664528</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1778201604396716</v>
+        <v>0.1797201604396716</v>
       </c>
       <c r="C59">
-        <v>-1.133761783833193</v>
+        <v>-1.1806706837555</v>
       </c>
       <c r="D59">
-        <v>0.8492582161668074</v>
+        <v>0.8372093162445003</v>
       </c>
       <c r="E59">
-        <v>1.87102</v>
+        <v>1.90588</v>
       </c>
       <c r="F59">
-        <v>1.98702</v>
+        <v>2.02188</v>
       </c>
       <c r="G59">
         <v>0.004</v>
@@ -6247,37 +6247,37 @@
         <v>0.136</v>
       </c>
       <c r="M59">
-        <v>0.4685393160000001</v>
+        <v>0.4767593040000001</v>
       </c>
       <c r="N59">
-        <v>-0.3325393160000001</v>
+        <v>-0.3407593040000001</v>
       </c>
       <c r="O59">
-        <v>-0.06318247004000002</v>
+        <v>-0.06474426776000002</v>
       </c>
       <c r="P59">
-        <v>-0.2693568459600001</v>
+        <v>-0.2760150362400001</v>
       </c>
       <c r="Q59">
-        <v>-0.1203568459600001</v>
+        <v>-0.12701503624</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1182015525842207</v>
+        <v>0.1199253990743211</v>
       </c>
       <c r="T59">
-        <v>1.326059861955031</v>
+        <v>1.357632715811103</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05515012106262604</v>
+        <v>0.05419925690637387</v>
       </c>
       <c r="W59">
-        <v>0.2227956014534328</v>
+        <v>0.2230198152214771</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2902637950664528</v>
+        <v>0.285259246875652</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1797201604396716</v>
+        <v>0.1816201604396716</v>
       </c>
       <c r="C60">
-        <v>-1.180670683755499</v>
+        <v>-1.227242477466501</v>
       </c>
       <c r="D60">
-        <v>0.8372093162445003</v>
+        <v>0.8254975225334988</v>
       </c>
       <c r="E60">
-        <v>1.90588</v>
+        <v>1.94074</v>
       </c>
       <c r="F60">
-        <v>2.02188</v>
+        <v>2.05674</v>
       </c>
       <c r="G60">
         <v>0.004</v>
@@ -6329,37 +6329,37 @@
         <v>0.136</v>
       </c>
       <c r="M60">
-        <v>0.476759304</v>
+        <v>0.484979292</v>
       </c>
       <c r="N60">
-        <v>-0.340759304</v>
+        <v>-0.348979292</v>
       </c>
       <c r="O60">
-        <v>-0.06474426776</v>
+        <v>-0.06630606548</v>
       </c>
       <c r="P60">
-        <v>-0.27601503624</v>
+        <v>-0.28267322652</v>
       </c>
       <c r="Q60">
-        <v>-0.12701503624</v>
+        <v>-0.13367322652</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1199253990743211</v>
+        <v>0.1217333356371094</v>
       </c>
       <c r="T60">
-        <v>1.357632715811103</v>
+        <v>1.390745708879666</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05419925690637387</v>
+        <v>0.05328062543338449</v>
       </c>
       <c r="W60">
-        <v>0.2230198152214771</v>
+        <v>0.223236428522808</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.285259246875652</v>
+        <v>0.2804243443862341</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1816201604396716</v>
+        <v>0.1835201604396716</v>
       </c>
       <c r="C61">
-        <v>-1.227242477466501</v>
+        <v>-1.273491117211085</v>
       </c>
       <c r="D61">
-        <v>0.8254975225334988</v>
+        <v>0.8141088827889155</v>
       </c>
       <c r="E61">
-        <v>1.94074</v>
+        <v>1.9756</v>
       </c>
       <c r="F61">
-        <v>2.05674</v>
+        <v>2.0916</v>
       </c>
       <c r="G61">
         <v>0.004</v>
@@ -6411,37 +6411,37 @@
         <v>0.136</v>
       </c>
       <c r="M61">
-        <v>0.484979292</v>
+        <v>0.4931992800000001</v>
       </c>
       <c r="N61">
-        <v>-0.348979292</v>
+        <v>-0.3571992800000001</v>
       </c>
       <c r="O61">
-        <v>-0.06630606548</v>
+        <v>-0.06786786320000002</v>
       </c>
       <c r="P61">
-        <v>-0.28267322652</v>
+        <v>-0.2893314168000001</v>
       </c>
       <c r="Q61">
-        <v>-0.13367322652</v>
+        <v>-0.1403314168000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1217333356371094</v>
+        <v>0.1236316690280372</v>
       </c>
       <c r="T61">
-        <v>1.390745708879666</v>
+        <v>1.425514351601658</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05328062543338449</v>
+        <v>0.05239261500949474</v>
       </c>
       <c r="W61">
-        <v>0.223236428522808</v>
+        <v>0.2234458213807611</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2804243443862341</v>
+        <v>0.2757506053131302</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1835201604396716</v>
+        <v>0.1854201604396715</v>
       </c>
       <c r="C62">
-        <v>-1.273491117211085</v>
+        <v>-1.319429795766015</v>
       </c>
       <c r="D62">
-        <v>0.8141088827889155</v>
+        <v>0.803030204233985</v>
       </c>
       <c r="E62">
-        <v>1.9756</v>
+        <v>2.01046</v>
       </c>
       <c r="F62">
-        <v>2.0916</v>
+        <v>2.12646</v>
       </c>
       <c r="G62">
         <v>0.004</v>
@@ -6493,37 +6493,37 @@
         <v>0.136</v>
       </c>
       <c r="M62">
-        <v>0.4931992800000001</v>
+        <v>0.501419268</v>
       </c>
       <c r="N62">
-        <v>-0.3571992800000001</v>
+        <v>-0.365419268</v>
       </c>
       <c r="O62">
-        <v>-0.06786786320000002</v>
+        <v>-0.06942966092000001</v>
       </c>
       <c r="P62">
-        <v>-0.2893314168000001</v>
+        <v>-0.29598960708</v>
       </c>
       <c r="Q62">
-        <v>-0.1403314168000001</v>
+        <v>-0.14698960708</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1236316690280372</v>
+        <v>0.1256273528492689</v>
       </c>
       <c r="T62">
-        <v>1.425514351601658</v>
+        <v>1.462066001642726</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05239261500949474</v>
+        <v>0.05153371968147024</v>
       </c>
       <c r="W62">
-        <v>0.2234458213807611</v>
+        <v>0.2236483488991093</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2757506053131302</v>
+        <v>0.2712301035866854</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1854201604396715</v>
+        <v>0.1873201604396716</v>
       </c>
       <c r="C63">
-        <v>-1.319429795766015</v>
+        <v>-1.365070997421697</v>
       </c>
       <c r="D63">
-        <v>0.803030204233985</v>
+        <v>0.7922490025783028</v>
       </c>
       <c r="E63">
-        <v>2.01046</v>
+        <v>2.04532</v>
       </c>
       <c r="F63">
-        <v>2.12646</v>
+        <v>2.16132</v>
       </c>
       <c r="G63">
         <v>0.004</v>
@@ -6575,37 +6575,37 @@
         <v>0.136</v>
       </c>
       <c r="M63">
-        <v>0.501419268</v>
+        <v>0.509639256</v>
       </c>
       <c r="N63">
-        <v>-0.365419268</v>
+        <v>-0.373639256</v>
       </c>
       <c r="O63">
-        <v>-0.06942966092000001</v>
+        <v>-0.07099145864</v>
       </c>
       <c r="P63">
-        <v>-0.29598960708</v>
+        <v>-0.30264779736</v>
       </c>
       <c r="Q63">
-        <v>-0.14698960708</v>
+        <v>-0.15364779736</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1256273528492689</v>
+        <v>0.1277280726610918</v>
       </c>
       <c r="T63">
-        <v>1.462066001642726</v>
+        <v>1.500541422738587</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05153371968147024</v>
+        <v>0.05070253065434975</v>
       </c>
       <c r="W63">
-        <v>0.2236483488991093</v>
+        <v>0.2238443432717044</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2712301035866854</v>
+        <v>0.2668554244965776</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1873201604396716</v>
+        <v>0.1892201604396716</v>
       </c>
       <c r="C64">
-        <v>-1.365070997421697</v>
+        <v>-1.410426544911563</v>
       </c>
       <c r="D64">
-        <v>0.7922490025783028</v>
+        <v>0.781753455088437</v>
       </c>
       <c r="E64">
-        <v>2.04532</v>
+        <v>2.08018</v>
       </c>
       <c r="F64">
-        <v>2.16132</v>
+        <v>2.19618</v>
       </c>
       <c r="G64">
         <v>0.004</v>
@@ -6657,37 +6657,37 @@
         <v>0.136</v>
       </c>
       <c r="M64">
-        <v>0.509639256</v>
+        <v>0.5178592440000001</v>
       </c>
       <c r="N64">
-        <v>-0.373639256</v>
+        <v>-0.381859244</v>
       </c>
       <c r="O64">
-        <v>-0.07099145864</v>
+        <v>-0.07255325636000001</v>
       </c>
       <c r="P64">
-        <v>-0.30264779736</v>
+        <v>-0.3093059876400001</v>
       </c>
       <c r="Q64">
-        <v>-0.15364779736</v>
+        <v>-0.16030598764</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1277280726610918</v>
+        <v>0.1299423448951753</v>
       </c>
       <c r="T64">
-        <v>1.500541422738587</v>
+        <v>1.541096596326116</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05070253065434975</v>
+        <v>0.04989772858047119</v>
       </c>
       <c r="W64">
-        <v>0.2238443432717044</v>
+        <v>0.2240341156007249</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2668554244965776</v>
+        <v>0.2626196241077431</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1892201604396716</v>
+        <v>0.1911201604396716</v>
       </c>
       <c r="C65">
-        <v>-1.410426544911563</v>
+        <v>-1.45550764265997</v>
       </c>
       <c r="D65">
-        <v>0.781753455088437</v>
+        <v>0.7715323573400303</v>
       </c>
       <c r="E65">
-        <v>2.08018</v>
+        <v>2.11504</v>
       </c>
       <c r="F65">
-        <v>2.19618</v>
+        <v>2.23104</v>
       </c>
       <c r="G65">
         <v>0.004</v>
@@ -6739,37 +6739,37 @@
         <v>0.136</v>
       </c>
       <c r="M65">
-        <v>0.5178592440000001</v>
+        <v>0.5260792320000001</v>
       </c>
       <c r="N65">
-        <v>-0.381859244</v>
+        <v>-0.3900792320000001</v>
       </c>
       <c r="O65">
-        <v>-0.07255325636000001</v>
+        <v>-0.07411505408000001</v>
       </c>
       <c r="P65">
-        <v>-0.3093059876400001</v>
+        <v>-0.31596417792</v>
       </c>
       <c r="Q65">
-        <v>-0.16030598764</v>
+        <v>-0.16696417792</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1299423448951753</v>
+        <v>0.1322796322533747</v>
       </c>
       <c r="T65">
-        <v>1.541096596326116</v>
+        <v>1.583904835112953</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04989772858047119</v>
+        <v>0.04911807657140132</v>
       </c>
       <c r="W65">
-        <v>0.2240341156007249</v>
+        <v>0.2242179575444636</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2626196241077431</v>
+        <v>0.2585161924810596</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1911201604396716</v>
+        <v>0.1930201604396716</v>
       </c>
       <c r="C66">
-        <v>-1.45550764265997</v>
+        <v>-1.500324916681192</v>
       </c>
       <c r="D66">
-        <v>0.7715323573400303</v>
+        <v>0.7615750833188082</v>
       </c>
       <c r="E66">
-        <v>2.11504</v>
+        <v>2.1499</v>
       </c>
       <c r="F66">
-        <v>2.23104</v>
+        <v>2.2659</v>
       </c>
       <c r="G66">
         <v>0.004</v>
@@ -6821,37 +6821,37 @@
         <v>0.136</v>
       </c>
       <c r="M66">
-        <v>0.5260792320000001</v>
+        <v>0.5342992200000001</v>
       </c>
       <c r="N66">
-        <v>-0.3900792320000001</v>
+        <v>-0.3982992200000001</v>
       </c>
       <c r="O66">
-        <v>-0.07411505408000001</v>
+        <v>-0.07567685180000001</v>
       </c>
       <c r="P66">
-        <v>-0.31596417792</v>
+        <v>-0.3226223682000001</v>
       </c>
       <c r="Q66">
-        <v>-0.16696417792</v>
+        <v>-0.1736223682</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1322796322533747</v>
+        <v>0.1347504788891854</v>
       </c>
       <c r="T66">
-        <v>1.583904835112953</v>
+        <v>1.629159258973323</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04911807657140132</v>
+        <v>0.04836241385491821</v>
       </c>
       <c r="W66">
-        <v>0.2242179575444636</v>
+        <v>0.2243961428130103</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2585161924810596</v>
+        <v>0.2545390202890433</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1930201604396716</v>
+        <v>0.1949201604396716</v>
       </c>
       <c r="C67">
-        <v>-1.500324916681192</v>
+        <v>-1.5448884514282</v>
       </c>
       <c r="D67">
-        <v>0.7615750833188082</v>
+        <v>0.7518715485718003</v>
       </c>
       <c r="E67">
-        <v>2.1499</v>
+        <v>2.18476</v>
       </c>
       <c r="F67">
-        <v>2.2659</v>
+        <v>2.30076</v>
       </c>
       <c r="G67">
         <v>0.004</v>
@@ -6903,37 +6903,37 @@
         <v>0.136</v>
       </c>
       <c r="M67">
-        <v>0.5342992200000001</v>
+        <v>0.5425192080000001</v>
       </c>
       <c r="N67">
-        <v>-0.3982992200000001</v>
+        <v>-0.4065192080000001</v>
       </c>
       <c r="O67">
-        <v>-0.07567685180000001</v>
+        <v>-0.07723864952000002</v>
       </c>
       <c r="P67">
-        <v>-0.3226223682000001</v>
+        <v>-0.32928055848</v>
       </c>
       <c r="Q67">
-        <v>-0.1736223682</v>
+        <v>-0.18028055848</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1347504788891854</v>
+        <v>0.1373666694447497</v>
       </c>
       <c r="T67">
-        <v>1.629159258973323</v>
+        <v>1.677075707766656</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04836241385491821</v>
+        <v>0.04762965000863158</v>
       </c>
       <c r="W67">
-        <v>0.2243961428130103</v>
+        <v>0.2245689285279647</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2545390202890433</v>
+        <v>0.250682368466482</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1949201604396716</v>
+        <v>0.1968201604396716</v>
       </c>
       <c r="C68">
-        <v>-1.5448884514282</v>
+        <v>-1.58920782385985</v>
       </c>
       <c r="D68">
-        <v>0.7518715485718003</v>
+        <v>0.7424121761401502</v>
       </c>
       <c r="E68">
-        <v>2.18476</v>
+        <v>2.21962</v>
       </c>
       <c r="F68">
-        <v>2.30076</v>
+        <v>2.33562</v>
       </c>
       <c r="G68">
         <v>0.004</v>
@@ -6985,37 +6985,37 @@
         <v>0.136</v>
       </c>
       <c r="M68">
-        <v>0.5425192080000001</v>
+        <v>0.5507391960000001</v>
       </c>
       <c r="N68">
-        <v>-0.4065192080000001</v>
+        <v>-0.4147391960000001</v>
       </c>
       <c r="O68">
-        <v>-0.07723864952000002</v>
+        <v>-0.07880044724000002</v>
       </c>
       <c r="P68">
-        <v>-0.32928055848</v>
+        <v>-0.3359387487600001</v>
       </c>
       <c r="Q68">
-        <v>-0.18028055848</v>
+        <v>-0.1869387487600001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1373666694447497</v>
+        <v>0.1401414170036815</v>
       </c>
       <c r="T68">
-        <v>1.677075707766656</v>
+        <v>1.727896183759585</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04762965000863158</v>
+        <v>0.04691875970999529</v>
       </c>
       <c r="W68">
-        <v>0.2245689285279647</v>
+        <v>0.2247365564603831</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.250682368466482</v>
+        <v>0.2469408405789225</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1968201604396716</v>
+        <v>0.1987201604396716</v>
       </c>
       <c r="C69">
-        <v>-1.58920782385985</v>
+        <v>-1.633292134968409</v>
       </c>
       <c r="D69">
-        <v>0.7424121761401502</v>
+        <v>0.7331878650315912</v>
       </c>
       <c r="E69">
-        <v>2.21962</v>
+        <v>2.25448</v>
       </c>
       <c r="F69">
-        <v>2.33562</v>
+        <v>2.37048</v>
       </c>
       <c r="G69">
         <v>0.004</v>
@@ -7067,37 +7067,37 @@
         <v>0.136</v>
       </c>
       <c r="M69">
-        <v>0.5507391960000001</v>
+        <v>0.5589591840000001</v>
       </c>
       <c r="N69">
-        <v>-0.4147391960000001</v>
+        <v>-0.4229591840000001</v>
       </c>
       <c r="O69">
-        <v>-0.07880044724000002</v>
+        <v>-0.08036224496000002</v>
       </c>
       <c r="P69">
-        <v>-0.3359387487600001</v>
+        <v>-0.3425969390400001</v>
       </c>
       <c r="Q69">
-        <v>-0.1869387487600001</v>
+        <v>-0.1935969390400001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1401414170036815</v>
+        <v>0.1430895862850465</v>
       </c>
       <c r="T69">
-        <v>1.727896183759585</v>
+        <v>1.781892939502073</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04691875970999529</v>
+        <v>0.04622877794955418</v>
       </c>
       <c r="W69">
-        <v>0.2247365564603831</v>
+        <v>0.2248992541594951</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2469408405789225</v>
+        <v>0.2433093576292326</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1987201604396716</v>
+        <v>0.2006201604396716</v>
       </c>
       <c r="C70">
-        <v>-1.633292134968409</v>
+        <v>-1.677150038985585</v>
       </c>
       <c r="D70">
-        <v>0.7331878650315912</v>
+        <v>0.7241899610144149</v>
       </c>
       <c r="E70">
-        <v>2.25448</v>
+        <v>2.28934</v>
       </c>
       <c r="F70">
-        <v>2.37048</v>
+        <v>2.40534</v>
       </c>
       <c r="G70">
         <v>0.004</v>
@@ -7149,37 +7149,37 @@
         <v>0.136</v>
       </c>
       <c r="M70">
-        <v>0.5589591840000001</v>
+        <v>0.5671791720000001</v>
       </c>
       <c r="N70">
-        <v>-0.4229591840000001</v>
+        <v>-0.4311791720000001</v>
       </c>
       <c r="O70">
-        <v>-0.08036224496000002</v>
+        <v>-0.08192404268000002</v>
       </c>
       <c r="P70">
-        <v>-0.3425969390400001</v>
+        <v>-0.3492551293200001</v>
       </c>
       <c r="Q70">
-        <v>-0.1935969390400001</v>
+        <v>-0.2002551293200001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1430895862850465</v>
+        <v>0.1462279600361771</v>
       </c>
       <c r="T70">
-        <v>1.781892939502073</v>
+        <v>1.839373356905365</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04622877794955418</v>
+        <v>0.0455587956604302</v>
       </c>
       <c r="W70">
-        <v>0.2248992541594951</v>
+        <v>0.2250572359832706</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2433093576292326</v>
+        <v>0.2397831350548958</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2006201604396716</v>
+        <v>0.2025201604396716</v>
       </c>
       <c r="C71">
-        <v>-1.677150038985585</v>
+        <v>-1.720789770464083</v>
       </c>
       <c r="D71">
-        <v>0.7241899610144149</v>
+        <v>0.715410229535917</v>
       </c>
       <c r="E71">
-        <v>2.28934</v>
+        <v>2.3242</v>
       </c>
       <c r="F71">
-        <v>2.40534</v>
+        <v>2.4402</v>
       </c>
       <c r="G71">
         <v>0.004</v>
@@ -7231,37 +7231,37 @@
         <v>0.136</v>
       </c>
       <c r="M71">
-        <v>0.5671791720000001</v>
+        <v>0.5753991600000001</v>
       </c>
       <c r="N71">
-        <v>-0.4311791720000001</v>
+        <v>-0.4393991600000001</v>
       </c>
       <c r="O71">
-        <v>-0.08192404268000002</v>
+        <v>-0.08348584040000002</v>
       </c>
       <c r="P71">
-        <v>-0.3492551293200001</v>
+        <v>-0.3559133196000001</v>
       </c>
       <c r="Q71">
-        <v>-0.2002551293200001</v>
+        <v>-0.2069133196000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1462279600361771</v>
+        <v>0.1495755587040496</v>
       </c>
       <c r="T71">
-        <v>1.839373356905365</v>
+        <v>1.900685802135544</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0455587956604302</v>
+        <v>0.04490795572242406</v>
       </c>
       <c r="W71">
-        <v>0.2250572359832706</v>
+        <v>0.2252107040406524</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2397831350548958</v>
+        <v>0.2363576616969687</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2025201604396716</v>
+        <v>0.2044201604396716</v>
       </c>
       <c r="C72">
-        <v>-1.720789770464083</v>
+        <v>-1.764219169412808</v>
       </c>
       <c r="D72">
-        <v>0.715410229535917</v>
+        <v>0.7068408305871923</v>
       </c>
       <c r="E72">
-        <v>2.3242</v>
+        <v>2.35906</v>
       </c>
       <c r="F72">
-        <v>2.4402</v>
+        <v>2.47506</v>
       </c>
       <c r="G72">
         <v>0.004</v>
@@ -7313,37 +7313,37 @@
         <v>0.136</v>
       </c>
       <c r="M72">
-        <v>0.5753991600000001</v>
+        <v>0.5836191480000001</v>
       </c>
       <c r="N72">
-        <v>-0.4393991600000001</v>
+        <v>-0.4476191480000001</v>
       </c>
       <c r="O72">
-        <v>-0.08348584040000002</v>
+        <v>-0.08504763812000003</v>
       </c>
       <c r="P72">
-        <v>-0.3559133196000001</v>
+        <v>-0.3625715098800001</v>
       </c>
       <c r="Q72">
-        <v>-0.2069133196000001</v>
+        <v>-0.2135715098800001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1495755587040496</v>
+        <v>0.1531540262455686</v>
       </c>
       <c r="T72">
-        <v>1.900685802135544</v>
+        <v>1.966226691864356</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04490795572242406</v>
+        <v>0.04427544930379836</v>
       </c>
       <c r="W72">
-        <v>0.2252107040406524</v>
+        <v>0.2253598490541644</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2363576616969687</v>
+        <v>0.2330286805463072</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2044201604396716</v>
+        <v>0.2063201604396716</v>
       </c>
       <c r="C73">
-        <v>-1.764219169412807</v>
+        <v>-1.807445704646993</v>
       </c>
       <c r="D73">
-        <v>0.706840830587193</v>
+        <v>0.6984742953530068</v>
       </c>
       <c r="E73">
-        <v>2.35906</v>
+        <v>2.39392</v>
       </c>
       <c r="F73">
-        <v>2.47506</v>
+        <v>2.50992</v>
       </c>
       <c r="G73">
         <v>0.004</v>
@@ -7395,37 +7395,37 @@
         <v>0.136</v>
       </c>
       <c r="M73">
-        <v>0.583619148</v>
+        <v>0.591839136</v>
       </c>
       <c r="N73">
-        <v>-0.447619148</v>
+        <v>-0.455839136</v>
       </c>
       <c r="O73">
-        <v>-0.08504763812</v>
+        <v>-0.08660943584000001</v>
       </c>
       <c r="P73">
-        <v>-0.36257150988</v>
+        <v>-0.36922970016</v>
       </c>
       <c r="Q73">
-        <v>-0.21357150988</v>
+        <v>-0.22022970016</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1531540262455685</v>
+        <v>0.1569880986114817</v>
       </c>
       <c r="T73">
-        <v>1.966226691864355</v>
+        <v>2.036449073716654</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04427544930379838</v>
+        <v>0.04366051250791229</v>
       </c>
       <c r="W73">
-        <v>0.2253598490541644</v>
+        <v>0.2255048511506343</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2330286805463072</v>
+        <v>0.2297921710942752</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2063201604396716</v>
+        <v>0.2082201604396716</v>
       </c>
       <c r="C74">
-        <v>-1.807445704646993</v>
+        <v>-1.850476495499424</v>
       </c>
       <c r="D74">
-        <v>0.6984742953530068</v>
+        <v>0.6903035045005763</v>
       </c>
       <c r="E74">
-        <v>2.39392</v>
+        <v>2.42878</v>
       </c>
       <c r="F74">
-        <v>2.50992</v>
+        <v>2.54478</v>
       </c>
       <c r="G74">
         <v>0.004</v>
@@ -7477,37 +7477,37 @@
         <v>0.136</v>
       </c>
       <c r="M74">
-        <v>0.591839136</v>
+        <v>0.6000591240000001</v>
       </c>
       <c r="N74">
-        <v>-0.455839136</v>
+        <v>-0.464059124</v>
       </c>
       <c r="O74">
-        <v>-0.08660943584000001</v>
+        <v>-0.08817123356000001</v>
       </c>
       <c r="P74">
-        <v>-0.36922970016</v>
+        <v>-0.37588789044</v>
       </c>
       <c r="Q74">
-        <v>-0.22022970016</v>
+        <v>-0.22688789044</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1569880986114817</v>
+        <v>0.1611061763378329</v>
       </c>
       <c r="T74">
-        <v>2.036449073716654</v>
+        <v>2.111873113483937</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04366051250791229</v>
+        <v>0.04306242329547513</v>
       </c>
       <c r="W74">
-        <v>0.2255048511506343</v>
+        <v>0.225645880586927</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2297921710942752</v>
+        <v>0.2266443331340796</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2082201604396716</v>
+        <v>0.2101201604396716</v>
       </c>
       <c r="C75">
-        <v>-1.850476495499424</v>
+        <v>-1.893318332025397</v>
       </c>
       <c r="D75">
-        <v>0.6903035045005763</v>
+        <v>0.6823216679746033</v>
       </c>
       <c r="E75">
-        <v>2.42878</v>
+        <v>2.46364</v>
       </c>
       <c r="F75">
-        <v>2.54478</v>
+        <v>2.57964</v>
       </c>
       <c r="G75">
         <v>0.004</v>
@@ -7559,37 +7559,37 @@
         <v>0.136</v>
       </c>
       <c r="M75">
-        <v>0.6000591240000001</v>
+        <v>0.608279112</v>
       </c>
       <c r="N75">
-        <v>-0.464059124</v>
+        <v>-0.4722791119999999</v>
       </c>
       <c r="O75">
-        <v>-0.08817123356000001</v>
+        <v>-0.08973303127999999</v>
       </c>
       <c r="P75">
-        <v>-0.37588789044</v>
+        <v>-0.38254608072</v>
       </c>
       <c r="Q75">
-        <v>-0.22688789044</v>
+        <v>-0.2335460807199999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1611061763378329</v>
+        <v>0.1655410292739034</v>
       </c>
       <c r="T75">
-        <v>2.111873113483937</v>
+        <v>2.193099002464089</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04306242329547513</v>
+        <v>0.04248049865634709</v>
       </c>
       <c r="W75">
-        <v>0.225645880586927</v>
+        <v>0.2257830984168334</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2266443331340796</v>
+        <v>0.223581571875511</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2101201604396716</v>
+        <v>0.2120201604396716</v>
       </c>
       <c r="C76">
-        <v>-1.893318332025397</v>
+        <v>-1.935977693821959</v>
       </c>
       <c r="D76">
-        <v>0.6823216679746033</v>
+        <v>0.6745223061780411</v>
       </c>
       <c r="E76">
-        <v>2.46364</v>
+        <v>2.4985</v>
       </c>
       <c r="F76">
-        <v>2.57964</v>
+        <v>2.6145</v>
       </c>
       <c r="G76">
         <v>0.004</v>
@@ -7641,37 +7641,37 @@
         <v>0.136</v>
       </c>
       <c r="M76">
-        <v>0.608279112</v>
+        <v>0.6164991000000001</v>
       </c>
       <c r="N76">
-        <v>-0.4722791119999999</v>
+        <v>-0.4804991000000001</v>
       </c>
       <c r="O76">
-        <v>-0.08973303127999999</v>
+        <v>-0.09129482900000001</v>
       </c>
       <c r="P76">
-        <v>-0.38254608072</v>
+        <v>-0.389204271</v>
       </c>
       <c r="Q76">
-        <v>-0.2335460807199999</v>
+        <v>-0.240204271</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1655410292739034</v>
+        <v>0.1703306704448595</v>
       </c>
       <c r="T76">
-        <v>2.193099002464089</v>
+        <v>2.280822962562652</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04248049865634709</v>
+        <v>0.04191409200759579</v>
       </c>
       <c r="W76">
-        <v>0.2257830984168334</v>
+        <v>0.2259166571046089</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.223581571875511</v>
+        <v>0.2206004842505042</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2120201604396716</v>
+        <v>0.2139201604396716</v>
       </c>
       <c r="C77">
-        <v>-1.935977693821959</v>
+        <v>-1.978460767571036</v>
       </c>
       <c r="D77">
-        <v>0.6745223061780411</v>
+        <v>0.6668992324289641</v>
       </c>
       <c r="E77">
-        <v>2.4985</v>
+        <v>2.53336</v>
       </c>
       <c r="F77">
-        <v>2.6145</v>
+        <v>2.64936</v>
       </c>
       <c r="G77">
         <v>0.004</v>
@@ -7723,37 +7723,37 @@
         <v>0.136</v>
       </c>
       <c r="M77">
-        <v>0.6164991000000001</v>
+        <v>0.6247190880000001</v>
       </c>
       <c r="N77">
-        <v>-0.4804991000000001</v>
+        <v>-0.4887190880000001</v>
       </c>
       <c r="O77">
-        <v>-0.09129482900000001</v>
+        <v>-0.09285662672000002</v>
       </c>
       <c r="P77">
-        <v>-0.389204271</v>
+        <v>-0.3958624612800001</v>
       </c>
       <c r="Q77">
-        <v>-0.240204271</v>
+        <v>-0.2468624612800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1703306704448595</v>
+        <v>0.175519448380062</v>
       </c>
       <c r="T77">
-        <v>2.280822962562652</v>
+        <v>2.37585725266943</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04191409200759579</v>
+        <v>0.04136259079696953</v>
       </c>
       <c r="W77">
-        <v>0.2259166571046089</v>
+        <v>0.2260467010900746</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2206004842505042</v>
+        <v>0.2176978462998397</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2139201604396716</v>
+        <v>0.2158201604396716</v>
       </c>
       <c r="C78">
-        <v>-1.978460767571036</v>
+        <v>-2.020773463406274</v>
       </c>
       <c r="D78">
-        <v>0.6668992324289641</v>
+        <v>0.6594465365937265</v>
       </c>
       <c r="E78">
-        <v>2.53336</v>
+        <v>2.56822</v>
       </c>
       <c r="F78">
-        <v>2.64936</v>
+        <v>2.68422</v>
       </c>
       <c r="G78">
         <v>0.004</v>
@@ -7805,37 +7805,37 @@
         <v>0.136</v>
       </c>
       <c r="M78">
-        <v>0.6247190880000001</v>
+        <v>0.6329390760000001</v>
       </c>
       <c r="N78">
-        <v>-0.4887190880000001</v>
+        <v>-0.4969390760000001</v>
       </c>
       <c r="O78">
-        <v>-0.09285662672000002</v>
+        <v>-0.09441842444000002</v>
       </c>
       <c r="P78">
-        <v>-0.3958624612800001</v>
+        <v>-0.4025206515600001</v>
       </c>
       <c r="Q78">
-        <v>-0.2468624612800001</v>
+        <v>-0.25352065156</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.175519448380062</v>
+        <v>0.1811594243965864</v>
       </c>
       <c r="T78">
-        <v>2.37585725266943</v>
+        <v>2.47915539408984</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04136259079696953</v>
+        <v>0.04082541429311278</v>
       </c>
       <c r="W78">
-        <v>0.2260467010900746</v>
+        <v>0.226173367309684</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2176978462998397</v>
+        <v>0.2148706015426989</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2158201604396716</v>
+        <v>0.2177201604396716</v>
       </c>
       <c r="C79">
-        <v>-2.020773463406274</v>
+        <v>-2.0629214301946</v>
       </c>
       <c r="D79">
-        <v>0.6594465365937265</v>
+        <v>0.6521585698054002</v>
       </c>
       <c r="E79">
-        <v>2.56822</v>
+        <v>2.60308</v>
       </c>
       <c r="F79">
-        <v>2.68422</v>
+        <v>2.71908</v>
       </c>
       <c r="G79">
         <v>0.004</v>
@@ -7887,37 +7887,37 @@
         <v>0.136</v>
       </c>
       <c r="M79">
-        <v>0.6329390760000001</v>
+        <v>0.6411590640000001</v>
       </c>
       <c r="N79">
-        <v>-0.4969390760000001</v>
+        <v>-0.5051590640000001</v>
       </c>
       <c r="O79">
-        <v>-0.09441842444000002</v>
+        <v>-0.09598022216000002</v>
       </c>
       <c r="P79">
-        <v>-0.4025206515600001</v>
+        <v>-0.4091788418400001</v>
       </c>
       <c r="Q79">
-        <v>-0.25352065156</v>
+        <v>-0.2601788418400001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1811594243965864</v>
+        <v>0.1873121255055222</v>
       </c>
       <c r="T79">
-        <v>2.47915539408984</v>
+        <v>2.591844275639378</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04082541429311278</v>
+        <v>0.04030201154576518</v>
       </c>
       <c r="W79">
-        <v>0.226173367309684</v>
+        <v>0.2262967856775086</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2148706015426989</v>
+        <v>0.2121158502408694</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2177201604396716</v>
+        <v>0.2196201604396716</v>
       </c>
       <c r="C80">
-        <v>-2.0629214301946</v>
+        <v>-2.104910069815551</v>
       </c>
       <c r="D80">
-        <v>0.6521585698054002</v>
+        <v>0.6450299301844495</v>
       </c>
       <c r="E80">
-        <v>2.60308</v>
+        <v>2.63794</v>
       </c>
       <c r="F80">
-        <v>2.71908</v>
+        <v>2.75394</v>
       </c>
       <c r="G80">
         <v>0.004</v>
@@ -7969,37 +7969,37 @@
         <v>0.136</v>
       </c>
       <c r="M80">
-        <v>0.6411590640000001</v>
+        <v>0.6493790520000001</v>
       </c>
       <c r="N80">
-        <v>-0.5051590640000001</v>
+        <v>-0.5133790520000001</v>
       </c>
       <c r="O80">
-        <v>-0.09598022216000002</v>
+        <v>-0.09754201988000002</v>
       </c>
       <c r="P80">
-        <v>-0.4091788418400001</v>
+        <v>-0.4158370321200001</v>
       </c>
       <c r="Q80">
-        <v>-0.2601788418400001</v>
+        <v>-0.2668370321200001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1873121255055222</v>
+        <v>0.1940507981486423</v>
       </c>
       <c r="T80">
-        <v>2.591844275639378</v>
+        <v>2.715265431622206</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04030201154576518</v>
+        <v>0.03979185950088208</v>
       </c>
       <c r="W80">
-        <v>0.2262967856775086</v>
+        <v>0.226417079529692</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2121158502408694</v>
+        <v>0.2094308394783267</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2196201604396716</v>
+        <v>0.2215201604396715</v>
       </c>
       <c r="C81">
-        <v>-2.104910069815551</v>
+        <v>-2.146744550514202</v>
       </c>
       <c r="D81">
-        <v>0.6450299301844495</v>
+        <v>0.638055449485798</v>
       </c>
       <c r="E81">
-        <v>2.63794</v>
+        <v>2.6728</v>
       </c>
       <c r="F81">
-        <v>2.75394</v>
+        <v>2.7888</v>
       </c>
       <c r="G81">
         <v>0.004</v>
@@ -8051,37 +8051,37 @@
         <v>0.136</v>
       </c>
       <c r="M81">
-        <v>0.6493790520000001</v>
+        <v>0.65759904</v>
       </c>
       <c r="N81">
-        <v>-0.5133790520000001</v>
+        <v>-0.52159904</v>
       </c>
       <c r="O81">
-        <v>-0.09754201988000002</v>
+        <v>-0.0991038176</v>
       </c>
       <c r="P81">
-        <v>-0.4158370321200001</v>
+        <v>-0.4224952224</v>
       </c>
       <c r="Q81">
-        <v>-0.2668370321200001</v>
+        <v>-0.2734952224</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1940507981486423</v>
+        <v>0.2014633380560744</v>
       </c>
       <c r="T81">
-        <v>2.715265431622206</v>
+        <v>2.851028703203316</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03979185950088208</v>
+        <v>0.03929446125712106</v>
       </c>
       <c r="W81">
-        <v>0.226417079529692</v>
+        <v>0.2265343660355708</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2094308394783267</v>
+        <v>0.2068129539848477</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2215201604396715</v>
+        <v>0.2234201604396716</v>
       </c>
       <c r="C82">
-        <v>-2.146744550514202</v>
+        <v>-2.188429819397093</v>
       </c>
       <c r="D82">
-        <v>0.638055449485798</v>
+        <v>0.6312301806029075</v>
       </c>
       <c r="E82">
-        <v>2.6728</v>
+        <v>2.70766</v>
       </c>
       <c r="F82">
-        <v>2.7888</v>
+        <v>2.82366</v>
       </c>
       <c r="G82">
         <v>0.004</v>
@@ -8133,37 +8133,37 @@
         <v>0.136</v>
       </c>
       <c r="M82">
-        <v>0.65759904</v>
+        <v>0.6658190280000001</v>
       </c>
       <c r="N82">
-        <v>-0.52159904</v>
+        <v>-0.5298190280000001</v>
       </c>
       <c r="O82">
-        <v>-0.0991038176</v>
+        <v>-0.10066561532</v>
       </c>
       <c r="P82">
-        <v>-0.4224952224</v>
+        <v>-0.4291534126800001</v>
       </c>
       <c r="Q82">
-        <v>-0.2734952224</v>
+        <v>-0.2801534126800001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2014633380560744</v>
+        <v>0.2096561453221836</v>
       </c>
       <c r="T82">
-        <v>2.851028703203316</v>
+        <v>3.001082845477175</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03929446125712106</v>
+        <v>0.03880934445147758</v>
       </c>
       <c r="W82">
-        <v>0.2265343660355708</v>
+        <v>0.2266487565783416</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2068129539848477</v>
+        <v>0.2042597076393556</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2234201604396716</v>
+        <v>0.2253201604396716</v>
       </c>
       <c r="C83">
-        <v>-2.188429819397093</v>
+        <v>-2.229970614134622</v>
       </c>
       <c r="D83">
-        <v>0.6312301806029075</v>
+        <v>0.6245493858653786</v>
       </c>
       <c r="E83">
-        <v>2.70766</v>
+        <v>2.74252</v>
       </c>
       <c r="F83">
-        <v>2.82366</v>
+        <v>2.85852</v>
       </c>
       <c r="G83">
         <v>0.004</v>
@@ -8215,37 +8215,37 @@
         <v>0.136</v>
       </c>
       <c r="M83">
-        <v>0.6658190280000001</v>
+        <v>0.6740390160000002</v>
       </c>
       <c r="N83">
-        <v>-0.5298190280000001</v>
+        <v>-0.5380390160000001</v>
       </c>
       <c r="O83">
-        <v>-0.10066561532</v>
+        <v>-0.10222741304</v>
       </c>
       <c r="P83">
-        <v>-0.4291534126800001</v>
+        <v>-0.4358116029600001</v>
       </c>
       <c r="Q83">
-        <v>-0.2801534126800001</v>
+        <v>-0.2868116029600001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2096561453221836</v>
+        <v>0.2187592645067494</v>
       </c>
       <c r="T83">
-        <v>3.001082845477175</v>
+        <v>3.167809670225907</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03880934445147758</v>
+        <v>0.03833605976304492</v>
       </c>
       <c r="W83">
-        <v>0.2266487565783416</v>
+        <v>0.226760357107874</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2042597076393556</v>
+        <v>0.2017687355949733</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2253201604396716</v>
+        <v>0.2272201604396716</v>
       </c>
       <c r="C84">
-        <v>-2.229970614134622</v>
+        <v>-2.271371473928089</v>
       </c>
       <c r="D84">
-        <v>0.6245493858653786</v>
+        <v>0.6180085260719114</v>
       </c>
       <c r="E84">
-        <v>2.74252</v>
+        <v>2.77738</v>
       </c>
       <c r="F84">
-        <v>2.85852</v>
+        <v>2.893380000000001</v>
       </c>
       <c r="G84">
         <v>0.004</v>
@@ -8297,37 +8297,37 @@
         <v>0.136</v>
       </c>
       <c r="M84">
-        <v>0.6740390160000002</v>
+        <v>0.6822590040000002</v>
       </c>
       <c r="N84">
-        <v>-0.5380390160000001</v>
+        <v>-0.5462590040000002</v>
       </c>
       <c r="O84">
-        <v>-0.10222741304</v>
+        <v>-0.10378921076</v>
       </c>
       <c r="P84">
-        <v>-0.4358116029600001</v>
+        <v>-0.4424697932400001</v>
       </c>
       <c r="Q84">
-        <v>-0.2868116029600001</v>
+        <v>-0.2934697932400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2187592645067494</v>
+        <v>0.2289333388894993</v>
       </c>
       <c r="T84">
-        <v>3.167809670225907</v>
+        <v>3.354151415533313</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03833605976304492</v>
+        <v>0.03787417952493595</v>
       </c>
       <c r="W84">
-        <v>0.226760357107874</v>
+        <v>0.2268692684680201</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2017687355949733</v>
+        <v>0.1993377869733471</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2272201604396716</v>
+        <v>0.2291201604396716</v>
       </c>
       <c r="C85">
-        <v>-2.271371473928089</v>
+        <v>-2.31263674979475</v>
       </c>
       <c r="D85">
-        <v>0.6180085260719114</v>
+        <v>0.6116032502052506</v>
       </c>
       <c r="E85">
-        <v>2.77738</v>
+        <v>2.812240000000001</v>
       </c>
       <c r="F85">
-        <v>2.893380000000001</v>
+        <v>2.928240000000001</v>
       </c>
       <c r="G85">
         <v>0.004</v>
@@ -8379,37 +8379,37 @@
         <v>0.136</v>
       </c>
       <c r="M85">
-        <v>0.6822590040000002</v>
+        <v>0.6904789920000002</v>
       </c>
       <c r="N85">
-        <v>-0.5462590040000002</v>
+        <v>-0.5544789920000002</v>
       </c>
       <c r="O85">
-        <v>-0.10378921076</v>
+        <v>-0.10535100848</v>
       </c>
       <c r="P85">
-        <v>-0.4424697932400001</v>
+        <v>-0.4491279835200002</v>
       </c>
       <c r="Q85">
-        <v>-0.2934697932400001</v>
+        <v>-0.3001279835200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2289333388894993</v>
+        <v>0.2403791725700931</v>
       </c>
       <c r="T85">
-        <v>3.354151415533313</v>
+        <v>3.563785879004147</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03787417952493595</v>
+        <v>0.03742329643535338</v>
       </c>
       <c r="W85">
-        <v>0.2268692684680201</v>
+        <v>0.2269755867005437</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1993377869733471</v>
+        <v>0.1969647180808073</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2291201604396716</v>
+        <v>0.2310201604396716</v>
       </c>
       <c r="C86">
-        <v>-2.312636749794749</v>
+        <v>-2.353770614219829</v>
       </c>
       <c r="D86">
-        <v>0.6116032502052514</v>
+        <v>0.6053293857801715</v>
       </c>
       <c r="E86">
-        <v>2.81224</v>
+        <v>2.8471</v>
       </c>
       <c r="F86">
-        <v>2.92824</v>
+        <v>2.9631</v>
       </c>
       <c r="G86">
         <v>0.004</v>
@@ -8461,37 +8461,37 @@
         <v>0.136</v>
       </c>
       <c r="M86">
-        <v>0.6904789920000001</v>
+        <v>0.6986989800000001</v>
       </c>
       <c r="N86">
-        <v>-0.5544789920000001</v>
+        <v>-0.5626989800000001</v>
       </c>
       <c r="O86">
-        <v>-0.10535100848</v>
+        <v>-0.1069128062</v>
       </c>
       <c r="P86">
-        <v>-0.4491279835200001</v>
+        <v>-0.4557861738000001</v>
       </c>
       <c r="Q86">
-        <v>-0.30012798352</v>
+        <v>-0.3067861738000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.240379172570093</v>
+        <v>0.2533511174080991</v>
       </c>
       <c r="T86">
-        <v>3.563785879004144</v>
+        <v>3.801371604271087</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03742329643535339</v>
+        <v>0.03698302235964335</v>
       </c>
       <c r="W86">
-        <v>0.2269755867005437</v>
+        <v>0.2270794033275961</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1969647180808073</v>
+        <v>0.194647486103386</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2310201604396716</v>
+        <v>0.2329201604396716</v>
       </c>
       <c r="C87">
-        <v>-2.353770614219829</v>
+        <v>-2.394777070220507</v>
       </c>
       <c r="D87">
-        <v>0.6053293857801715</v>
+        <v>0.5991829297794929</v>
       </c>
       <c r="E87">
-        <v>2.8471</v>
+        <v>2.88196</v>
       </c>
       <c r="F87">
-        <v>2.9631</v>
+        <v>2.99796</v>
       </c>
       <c r="G87">
         <v>0.004</v>
@@ -8543,37 +8543,37 @@
         <v>0.136</v>
       </c>
       <c r="M87">
-        <v>0.6986989800000001</v>
+        <v>0.706918968</v>
       </c>
       <c r="N87">
-        <v>-0.5626989800000001</v>
+        <v>-0.570918968</v>
       </c>
       <c r="O87">
-        <v>-0.1069128062</v>
+        <v>-0.10847460392</v>
       </c>
       <c r="P87">
-        <v>-0.4557861738000001</v>
+        <v>-0.46244436408</v>
       </c>
       <c r="Q87">
-        <v>-0.3067861738000001</v>
+        <v>-0.31344436408</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2533511174080991</v>
+        <v>0.2681761972229634</v>
       </c>
       <c r="T87">
-        <v>3.801371604271087</v>
+        <v>4.072898147433308</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03698302235964335</v>
+        <v>0.03655298721592657</v>
       </c>
       <c r="W87">
-        <v>0.2270794033275961</v>
+        <v>0.2271808056144845</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.194647486103386</v>
+        <v>0.1923841432417188</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2329201604396716</v>
+        <v>0.2348201604396715</v>
       </c>
       <c r="C88">
-        <v>-2.394777070220507</v>
+        <v>-2.435659959863246</v>
       </c>
       <c r="D88">
-        <v>0.5991829297794929</v>
+        <v>0.5931600401367541</v>
       </c>
       <c r="E88">
-        <v>2.88196</v>
+        <v>2.91682</v>
       </c>
       <c r="F88">
-        <v>2.99796</v>
+        <v>3.03282</v>
       </c>
       <c r="G88">
         <v>0.004</v>
@@ -8625,37 +8625,37 @@
         <v>0.136</v>
       </c>
       <c r="M88">
-        <v>0.706918968</v>
+        <v>0.715138956</v>
       </c>
       <c r="N88">
-        <v>-0.570918968</v>
+        <v>-0.579138956</v>
       </c>
       <c r="O88">
-        <v>-0.10847460392</v>
+        <v>-0.11003640164</v>
       </c>
       <c r="P88">
-        <v>-0.46244436408</v>
+        <v>-0.46910255436</v>
       </c>
       <c r="Q88">
-        <v>-0.31344436408</v>
+        <v>-0.32010255436</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2681761972229634</v>
+        <v>0.2852820585478067</v>
       </c>
       <c r="T88">
-        <v>4.072898147433308</v>
+        <v>4.386198004928177</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03655298721592657</v>
+        <v>0.03613283793758259</v>
       </c>
       <c r="W88">
-        <v>0.2271808056144845</v>
+        <v>0.227279876814318</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1923841432417188</v>
+        <v>0.1901728312504346</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2348201604396715</v>
+        <v>0.2367201604396716</v>
       </c>
       <c r="C89">
-        <v>-2.435659959863246</v>
+        <v>-2.476422972272541</v>
       </c>
       <c r="D89">
-        <v>0.5931600401367541</v>
+        <v>0.587257027727459</v>
       </c>
       <c r="E89">
-        <v>2.91682</v>
+        <v>2.95168</v>
       </c>
       <c r="F89">
-        <v>3.03282</v>
+        <v>3.06768</v>
       </c>
       <c r="G89">
         <v>0.004</v>
@@ -8707,37 +8707,37 @@
         <v>0.136</v>
       </c>
       <c r="M89">
-        <v>0.715138956</v>
+        <v>0.7233589440000001</v>
       </c>
       <c r="N89">
-        <v>-0.579138956</v>
+        <v>-0.5873589440000001</v>
       </c>
       <c r="O89">
-        <v>-0.11003640164</v>
+        <v>-0.11159819936</v>
       </c>
       <c r="P89">
-        <v>-0.46910255436</v>
+        <v>-0.4757607446400001</v>
       </c>
       <c r="Q89">
-        <v>-0.32010255436</v>
+        <v>-0.32676074464</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2852820585478067</v>
+        <v>0.305238896760124</v>
       </c>
       <c r="T89">
-        <v>4.386198004928177</v>
+        <v>4.751714505338859</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03613283793758259</v>
+        <v>0.03572223750647369</v>
       </c>
       <c r="W89">
-        <v>0.227279876814318</v>
+        <v>0.2273766963959735</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1901728312504346</v>
+        <v>0.1880117763498615</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2367201604396716</v>
+        <v>0.2386201604396716</v>
       </c>
       <c r="C90">
-        <v>-2.476422972272541</v>
+        <v>-2.517069651166169</v>
       </c>
       <c r="D90">
-        <v>0.587257027727459</v>
+        <v>0.5814703488338313</v>
       </c>
       <c r="E90">
-        <v>2.95168</v>
+        <v>2.98654</v>
       </c>
       <c r="F90">
-        <v>3.06768</v>
+        <v>3.10254</v>
       </c>
       <c r="G90">
         <v>0.004</v>
@@ -8789,37 +8789,37 @@
         <v>0.136</v>
       </c>
       <c r="M90">
-        <v>0.7233589440000001</v>
+        <v>0.7315789320000001</v>
       </c>
       <c r="N90">
-        <v>-0.5873589440000001</v>
+        <v>-0.5955789320000001</v>
       </c>
       <c r="O90">
-        <v>-0.11159819936</v>
+        <v>-0.11315999708</v>
       </c>
       <c r="P90">
-        <v>-0.4757607446400001</v>
+        <v>-0.4824189349200001</v>
       </c>
       <c r="Q90">
-        <v>-0.32676074464</v>
+        <v>-0.3334189349200001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.305238896760124</v>
+        <v>0.3288242510110443</v>
       </c>
       <c r="T90">
-        <v>4.751714505338859</v>
+        <v>5.183688551278756</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03572223750647369</v>
+        <v>0.03532086405134477</v>
       </c>
       <c r="W90">
-        <v>0.2273766963959735</v>
+        <v>0.2274713402566929</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1880117763498615</v>
+        <v>0.185899284480762</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2386201604396716</v>
+        <v>0.2405201604396716</v>
       </c>
       <c r="C91">
-        <v>-2.517069651166169</v>
+        <v>-2.557603401949291</v>
       </c>
       <c r="D91">
-        <v>0.5814703488338313</v>
+        <v>0.5757965980507093</v>
       </c>
       <c r="E91">
-        <v>2.98654</v>
+        <v>3.0214</v>
       </c>
       <c r="F91">
-        <v>3.10254</v>
+        <v>3.1374</v>
       </c>
       <c r="G91">
         <v>0.004</v>
@@ -8871,37 +8871,37 @@
         <v>0.136</v>
       </c>
       <c r="M91">
-        <v>0.7315789320000001</v>
+        <v>0.7397989200000001</v>
       </c>
       <c r="N91">
-        <v>-0.5955789320000001</v>
+        <v>-0.6037989200000001</v>
       </c>
       <c r="O91">
-        <v>-0.11315999708</v>
+        <v>-0.1147217948</v>
       </c>
       <c r="P91">
-        <v>-0.4824189349200001</v>
+        <v>-0.4890771252000001</v>
       </c>
       <c r="Q91">
-        <v>-0.3334189349200001</v>
+        <v>-0.3400771252000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3288242510110443</v>
+        <v>0.3571266761121488</v>
       </c>
       <c r="T91">
-        <v>5.183688551278756</v>
+        <v>5.702057406406632</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03532086405134477</v>
+        <v>0.03492841000632983</v>
       </c>
       <c r="W91">
-        <v>0.2274713402566929</v>
+        <v>0.2275638809205074</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.185899284480762</v>
+        <v>0.1838337368754202</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2405201604396716</v>
+        <v>0.2424201604396716</v>
       </c>
       <c r="C92">
-        <v>-2.557603401949291</v>
+        <v>-2.598027498397234</v>
       </c>
       <c r="D92">
-        <v>0.5757965980507093</v>
+        <v>0.5702325016027662</v>
       </c>
       <c r="E92">
-        <v>3.0214</v>
+        <v>3.05626</v>
       </c>
       <c r="F92">
-        <v>3.1374</v>
+        <v>3.17226</v>
       </c>
       <c r="G92">
         <v>0.004</v>
@@ -8953,37 +8953,37 @@
         <v>0.136</v>
       </c>
       <c r="M92">
-        <v>0.7397989200000001</v>
+        <v>0.748018908</v>
       </c>
       <c r="N92">
-        <v>-0.6037989200000001</v>
+        <v>-0.612018908</v>
       </c>
       <c r="O92">
-        <v>-0.1147217948</v>
+        <v>-0.11628359252</v>
       </c>
       <c r="P92">
-        <v>-0.4890771252000001</v>
+        <v>-0.49573531548</v>
       </c>
       <c r="Q92">
-        <v>-0.3400771252000001</v>
+        <v>-0.34673531548</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3571266761121488</v>
+        <v>0.3917185290134987</v>
       </c>
       <c r="T92">
-        <v>5.702057406406632</v>
+        <v>6.335619340451815</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03492841000632983</v>
+        <v>0.03454458132494159</v>
       </c>
       <c r="W92">
-        <v>0.2275638809205074</v>
+        <v>0.2276543877235788</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1838337368754202</v>
+        <v>0.1818135859207453</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2424201604396716</v>
+        <v>0.2443201604396716</v>
       </c>
       <c r="C93">
-        <v>-2.598027498397234</v>
+        <v>-2.638345088954514</v>
       </c>
       <c r="D93">
-        <v>0.5702325016027662</v>
+        <v>0.5647749110454862</v>
       </c>
       <c r="E93">
-        <v>3.05626</v>
+        <v>3.09112</v>
       </c>
       <c r="F93">
-        <v>3.17226</v>
+        <v>3.20712</v>
       </c>
       <c r="G93">
         <v>0.004</v>
@@ -9035,37 +9035,37 @@
         <v>0.136</v>
       </c>
       <c r="M93">
-        <v>0.748018908</v>
+        <v>0.756238896</v>
       </c>
       <c r="N93">
-        <v>-0.612018908</v>
+        <v>-0.620238896</v>
       </c>
       <c r="O93">
-        <v>-0.11628359252</v>
+        <v>-0.11784539024</v>
       </c>
       <c r="P93">
-        <v>-0.49573531548</v>
+        <v>-0.50239350576</v>
       </c>
       <c r="Q93">
-        <v>-0.34673531548</v>
+        <v>-0.3533935057599999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3917185290134987</v>
+        <v>0.4349583451401862</v>
       </c>
       <c r="T93">
-        <v>6.335619340451815</v>
+        <v>7.127571758008292</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03454458132494159</v>
+        <v>0.03416909674532266</v>
       </c>
       <c r="W93">
-        <v>0.2276543877235788</v>
+        <v>0.2277429269874529</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1818135859207453</v>
+        <v>0.1798373512911718</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2443201604396716</v>
+        <v>0.2462201604396716</v>
       </c>
       <c r="C94">
-        <v>-2.638345088954514</v>
+        <v>-2.67855920267557</v>
       </c>
       <c r="D94">
-        <v>0.5647749110454862</v>
+        <v>0.5594207973244298</v>
       </c>
       <c r="E94">
-        <v>3.09112</v>
+        <v>3.12598</v>
       </c>
       <c r="F94">
-        <v>3.20712</v>
+        <v>3.24198</v>
       </c>
       <c r="G94">
         <v>0.004</v>
@@ -9117,37 +9117,37 @@
         <v>0.136</v>
       </c>
       <c r="M94">
-        <v>0.756238896</v>
+        <v>0.7644588840000001</v>
       </c>
       <c r="N94">
-        <v>-0.620238896</v>
+        <v>-0.6284588840000001</v>
       </c>
       <c r="O94">
-        <v>-0.11784539024</v>
+        <v>-0.11940718796</v>
       </c>
       <c r="P94">
-        <v>-0.50239350576</v>
+        <v>-0.50905169604</v>
       </c>
       <c r="Q94">
-        <v>-0.3533935057599999</v>
+        <v>-0.36005169604</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4349583451401862</v>
+        <v>0.4905523944459271</v>
       </c>
       <c r="T94">
-        <v>7.127571758008292</v>
+        <v>8.145796294866621</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03416909674532266</v>
+        <v>0.03380168710289983</v>
       </c>
       <c r="W94">
-        <v>0.2277429269874529</v>
+        <v>0.2278295621811362</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1798373512911718</v>
+        <v>0.1779036163310518</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2462201604396716</v>
+        <v>0.2481201604396716</v>
       </c>
       <c r="C95">
-        <v>-2.67855920267557</v>
+        <v>-2.718672754830762</v>
       </c>
       <c r="D95">
-        <v>0.5594207973244298</v>
+        <v>0.5541672451692385</v>
       </c>
       <c r="E95">
-        <v>3.12598</v>
+        <v>3.16084</v>
       </c>
       <c r="F95">
-        <v>3.24198</v>
+        <v>3.27684</v>
       </c>
       <c r="G95">
         <v>0.004</v>
@@ -9199,37 +9199,37 @@
         <v>0.136</v>
       </c>
       <c r="M95">
-        <v>0.7644588840000001</v>
+        <v>0.7726788720000002</v>
       </c>
       <c r="N95">
-        <v>-0.6284588840000001</v>
+        <v>-0.6366788720000002</v>
       </c>
       <c r="O95">
-        <v>-0.11940718796</v>
+        <v>-0.12096898568</v>
       </c>
       <c r="P95">
-        <v>-0.50905169604</v>
+        <v>-0.5157098863200001</v>
       </c>
       <c r="Q95">
-        <v>-0.36005169604</v>
+        <v>-0.3667098863200001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4905523944459271</v>
+        <v>0.5646777935202484</v>
       </c>
       <c r="T95">
-        <v>8.145796294866621</v>
+        <v>9.503429010677728</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03380168710289983</v>
+        <v>0.03344209468691153</v>
       </c>
       <c r="W95">
-        <v>0.2278295621811362</v>
+        <v>0.2279143540728263</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1779036163310518</v>
+        <v>0.1760110246679555</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2481201604396716</v>
+        <v>0.2500201604396716</v>
       </c>
       <c r="C96">
-        <v>-2.718672754830762</v>
+        <v>-2.758688552199419</v>
       </c>
       <c r="D96">
-        <v>0.5541672451692385</v>
+        <v>0.5490114478005816</v>
       </c>
       <c r="E96">
-        <v>3.16084</v>
+        <v>3.1957</v>
       </c>
       <c r="F96">
-        <v>3.27684</v>
+        <v>3.311700000000001</v>
       </c>
       <c r="G96">
         <v>0.004</v>
@@ -9281,37 +9281,37 @@
         <v>0.136</v>
       </c>
       <c r="M96">
-        <v>0.7726788720000002</v>
+        <v>0.7808988600000002</v>
       </c>
       <c r="N96">
-        <v>-0.6366788720000002</v>
+        <v>-0.6448988600000002</v>
       </c>
       <c r="O96">
-        <v>-0.12096898568</v>
+        <v>-0.1225307834</v>
       </c>
       <c r="P96">
-        <v>-0.5157098863200001</v>
+        <v>-0.5223680766000002</v>
       </c>
       <c r="Q96">
-        <v>-0.3667098863200001</v>
+        <v>-0.3733680766000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5646777935202484</v>
+        <v>0.6684533522242984</v>
       </c>
       <c r="T96">
-        <v>9.503429010677728</v>
+        <v>11.40411481281328</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03344209468691153</v>
+        <v>0.03309007263757562</v>
       </c>
       <c r="W96">
-        <v>0.2279143540728263</v>
+        <v>0.2279973608720597</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1760110246679555</v>
+        <v>0.1741582770398716</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2500201604396716</v>
+        <v>0.2519201604396716</v>
       </c>
       <c r="C97">
-        <v>-2.758688552199419</v>
+        <v>-2.798609298070158</v>
       </c>
       <c r="D97">
-        <v>0.5490114478005816</v>
+        <v>0.5439507019298429</v>
       </c>
       <c r="E97">
-        <v>3.1957</v>
+        <v>3.230560000000001</v>
       </c>
       <c r="F97">
-        <v>3.311700000000001</v>
+        <v>3.346560000000001</v>
       </c>
       <c r="G97">
         <v>0.004</v>
@@ -9363,37 +9363,37 @@
         <v>0.136</v>
       </c>
       <c r="M97">
-        <v>0.7808988600000002</v>
+        <v>0.7891188480000002</v>
       </c>
       <c r="N97">
-        <v>-0.6448988600000002</v>
+        <v>-0.6531188480000002</v>
       </c>
       <c r="O97">
-        <v>-0.1225307834</v>
+        <v>-0.12409258112</v>
       </c>
       <c r="P97">
-        <v>-0.5223680766000002</v>
+        <v>-0.5290262668800001</v>
       </c>
       <c r="Q97">
-        <v>-0.3733680766000002</v>
+        <v>-0.3800262668800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6684533522242984</v>
+        <v>0.8241166902803733</v>
       </c>
       <c r="T97">
-        <v>11.40411481281328</v>
+        <v>14.2551435160166</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03309007263757562</v>
+        <v>0.03274538438093421</v>
       </c>
       <c r="W97">
-        <v>0.2279973608720597</v>
+        <v>0.2280786383629757</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1741582770398716</v>
+        <v>0.1723441283207063</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2519201604396716</v>
+        <v>0.2538201604396716</v>
       </c>
       <c r="C98">
-        <v>-2.798609298070157</v>
+        <v>-2.83843759696716</v>
       </c>
       <c r="D98">
-        <v>0.5439507019298429</v>
+        <v>0.5389824030328403</v>
       </c>
       <c r="E98">
-        <v>3.23056</v>
+        <v>3.26542</v>
       </c>
       <c r="F98">
-        <v>3.34656</v>
+        <v>3.38142</v>
       </c>
       <c r="G98">
         <v>0.004</v>
@@ -9445,37 +9445,37 @@
         <v>0.136</v>
       </c>
       <c r="M98">
-        <v>0.7891188480000001</v>
+        <v>0.7973388360000001</v>
       </c>
       <c r="N98">
-        <v>-0.6531188480000001</v>
+        <v>-0.6613388360000001</v>
       </c>
       <c r="O98">
-        <v>-0.12409258112</v>
+        <v>-0.12565437884</v>
       </c>
       <c r="P98">
-        <v>-0.5290262668800001</v>
+        <v>-0.5356844571600001</v>
       </c>
       <c r="Q98">
-        <v>-0.3800262668800001</v>
+        <v>-0.3866844571600001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8241166902803713</v>
+        <v>1.083555587040495</v>
       </c>
       <c r="T98">
-        <v>14.25514351601657</v>
+        <v>19.00685802135542</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03274538438093422</v>
+        <v>0.03240780309865654</v>
       </c>
       <c r="W98">
-        <v>0.2280786383629757</v>
+        <v>0.2281582400293368</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1723441283207063</v>
+        <v>0.1705673847297713</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2538201604396716</v>
+        <v>0.2557201604396716</v>
       </c>
       <c r="C99">
-        <v>-2.83843759696716</v>
+        <v>-2.878175959119787</v>
       </c>
       <c r="D99">
-        <v>0.5389824030328403</v>
+        <v>0.5341040408802129</v>
       </c>
       <c r="E99">
-        <v>3.26542</v>
+        <v>3.30028</v>
       </c>
       <c r="F99">
-        <v>3.38142</v>
+        <v>3.41628</v>
       </c>
       <c r="G99">
         <v>0.004</v>
@@ -9527,37 +9527,37 @@
         <v>0.136</v>
       </c>
       <c r="M99">
-        <v>0.7973388360000001</v>
+        <v>0.805558824</v>
       </c>
       <c r="N99">
-        <v>-0.6613388360000001</v>
+        <v>-0.669558824</v>
       </c>
       <c r="O99">
-        <v>-0.12565437884</v>
+        <v>-0.12721617656</v>
       </c>
       <c r="P99">
-        <v>-0.5356844571600001</v>
+        <v>-0.5423426474399999</v>
       </c>
       <c r="Q99">
-        <v>-0.3866844571600001</v>
+        <v>-0.3933426474399999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.083555587040495</v>
+        <v>1.602433380560743</v>
       </c>
       <c r="T99">
-        <v>19.00685802135542</v>
+        <v>28.51028703203313</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03240780309865654</v>
+        <v>0.03207711123030291</v>
       </c>
       <c r="W99">
-        <v>0.2281582400293368</v>
+        <v>0.2282362171718946</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1705673847297713</v>
+        <v>0.1688269012121205</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2557201604396716</v>
+        <v>0.2576201604396716</v>
       </c>
       <c r="C100">
-        <v>-2.878175959119787</v>
+        <v>-2.917826804691644</v>
       </c>
       <c r="D100">
-        <v>0.5341040408802129</v>
+        <v>0.5293131953083559</v>
       </c>
       <c r="E100">
-        <v>3.30028</v>
+        <v>3.33514</v>
       </c>
       <c r="F100">
-        <v>3.41628</v>
+        <v>3.45114</v>
       </c>
       <c r="G100">
         <v>0.004</v>
@@ -9609,37 +9609,37 @@
         <v>0.136</v>
       </c>
       <c r="M100">
-        <v>0.805558824</v>
+        <v>0.813778812</v>
       </c>
       <c r="N100">
-        <v>-0.669558824</v>
+        <v>-0.677778812</v>
       </c>
       <c r="O100">
-        <v>-0.12721617656</v>
+        <v>-0.12877797428</v>
       </c>
       <c r="P100">
-        <v>-0.5423426474399999</v>
+        <v>-0.54900083772</v>
       </c>
       <c r="Q100">
-        <v>-0.3933426474399999</v>
+        <v>-0.4000008377199999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.602433380560743</v>
+        <v>3.159066761121485</v>
       </c>
       <c r="T100">
-        <v>28.51028703203313</v>
+        <v>57.02057406406627</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03207711123030291</v>
+        <v>0.0317531000057544</v>
       </c>
       <c r="W100">
-        <v>0.2282362171718946</v>
+        <v>0.2283126190186431</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1688269012121205</v>
+        <v>0.1671215789776547</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2576201604396716</v>
-      </c>
-      <c r="C101">
-        <v>-2.917826804691644</v>
-      </c>
-      <c r="D101">
-        <v>0.5293131953083559</v>
-      </c>
-      <c r="E101">
-        <v>3.33514</v>
-      </c>
-      <c r="F101">
-        <v>3.45114</v>
-      </c>
-      <c r="G101">
-        <v>0.004</v>
-      </c>
-      <c r="H101">
-        <v>3.37</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.285</v>
-      </c>
-      <c r="K101">
-        <v>0.149</v>
-      </c>
-      <c r="L101">
-        <v>0.136</v>
-      </c>
-      <c r="M101">
-        <v>0.813778812</v>
-      </c>
-      <c r="N101">
-        <v>-0.677778812</v>
-      </c>
-      <c r="O101">
-        <v>-0.12877797428</v>
-      </c>
-      <c r="P101">
-        <v>-0.54900083772</v>
-      </c>
-      <c r="Q101">
-        <v>-0.4000008377199999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.159066761121485</v>
-      </c>
-      <c r="T101">
-        <v>57.02057406406627</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0317531000057544</v>
-      </c>
-      <c r="W101">
-        <v>0.2283126190186431</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1671215789776547</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
